--- a/dcor-wpac-final/results-raw/merged/dcor_wpac_full_merged_tracker_01_initial.xlsx
+++ b/dcor-wpac-final/results-raw/merged/dcor_wpac_full_merged_tracker_01_initial.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="464">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="460">
   <si>
     <t xml:space="preserve">Stage</t>
   </si>
@@ -190,9 +190,6 @@
     <t xml:space="preserve">z0012513</t>
   </si>
   <si>
-    <t xml:space="preserve">z0012514</t>
-  </si>
-  <si>
     <t xml:space="preserve">z0012515</t>
   </si>
   <si>
@@ -340,12 +337,6 @@
     <t xml:space="preserve">z0040942</t>
   </si>
   <si>
-    <t xml:space="preserve">z0040943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">z0040945</t>
-  </si>
-  <si>
     <t xml:space="preserve">z0061449</t>
   </si>
   <si>
@@ -370,9 +361,6 @@
     <t xml:space="preserve">z0061462</t>
   </si>
   <si>
-    <t xml:space="preserve">z0061464</t>
-  </si>
-  <si>
     <t xml:space="preserve">z0061467</t>
   </si>
   <si>
@@ -910,12 +898,12 @@
     <t xml:space="preserve">locus137</t>
   </si>
   <si>
+    <t xml:space="preserve">locus120</t>
+  </si>
+  <si>
     <t xml:space="preserve">locus165</t>
   </si>
   <si>
-    <t xml:space="preserve">locus120</t>
-  </si>
-  <si>
     <t xml:space="preserve">locus192</t>
   </si>
   <si>
@@ -1180,12 +1168,12 @@
     <t xml:space="preserve">Dc33907</t>
   </si>
   <si>
+    <t xml:space="preserve">locus035</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dc36571</t>
   </si>
   <si>
-    <t xml:space="preserve">locus035</t>
-  </si>
-  <si>
     <t xml:space="preserve">locus039</t>
   </si>
   <si>
@@ -1201,12 +1189,12 @@
     <t xml:space="preserve">Dc28776</t>
   </si>
   <si>
+    <t xml:space="preserve">locus134</t>
+  </si>
+  <si>
     <t xml:space="preserve">locus227</t>
   </si>
   <si>
-    <t xml:space="preserve">locus134</t>
-  </si>
-  <si>
     <t xml:space="preserve">locus256</t>
   </si>
   <si>
@@ -1285,15 +1273,15 @@
     <t xml:space="preserve">Dc10878</t>
   </si>
   <si>
+    <t xml:space="preserve">locus360</t>
+  </si>
+  <si>
+    <t xml:space="preserve">locus076</t>
+  </si>
+  <si>
     <t xml:space="preserve">locus231</t>
   </si>
   <si>
-    <t xml:space="preserve">locus076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">locus360</t>
-  </si>
-  <si>
     <t xml:space="preserve">locus188</t>
   </si>
   <si>
@@ -1309,12 +1297,12 @@
     <t xml:space="preserve">Dc22883</t>
   </si>
   <si>
+    <t xml:space="preserve">Dc08578</t>
+  </si>
+  <si>
     <t xml:space="preserve">locus255</t>
   </si>
   <si>
-    <t xml:space="preserve">Dc08578</t>
-  </si>
-  <si>
     <t xml:space="preserve">Dc00544</t>
   </si>
   <si>
@@ -1324,10 +1312,10 @@
     <t xml:space="preserve">Dc06503</t>
   </si>
   <si>
+    <t xml:space="preserve">Dc36767</t>
+  </si>
+  <si>
     <t xml:space="preserve">locus334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Dc36767</t>
   </si>
   <si>
     <t xml:space="preserve">Dc11062</t>
@@ -1770,7 +1758,7 @@
       <c r="C2"/>
       <c r="D2"/>
       <c r="E2" t="n">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -2233,10 +2221,10 @@
         <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>145</v>
+        <v>177</v>
       </c>
       <c r="D27" t="n">
-        <v>0.792349726775956</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E27" t="s">
         <v>16</v>
@@ -2501,10 +2489,10 @@
         <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>173</v>
+        <v>134</v>
       </c>
       <c r="D43" t="n">
-        <v>0.945355191256831</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E43" t="s">
         <v>16</v>
@@ -2518,10 +2506,10 @@
         <v>15</v>
       </c>
       <c r="C44" t="n">
-        <v>134</v>
+        <v>171</v>
       </c>
       <c r="D44" t="n">
-        <v>0.73224043715847</v>
+        <v>0.934426229508197</v>
       </c>
       <c r="E44" t="s">
         <v>16</v>
@@ -2535,10 +2523,10 @@
         <v>15</v>
       </c>
       <c r="C45" t="n">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="D45" t="n">
-        <v>0.934426229508197</v>
+        <v>0.808743169398907</v>
       </c>
       <c r="E45" t="s">
         <v>16</v>
@@ -2552,10 +2540,10 @@
         <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="D46" t="n">
-        <v>0.808743169398907</v>
+        <v>0.759562841530055</v>
       </c>
       <c r="E46" t="s">
         <v>16</v>
@@ -2569,10 +2557,10 @@
         <v>15</v>
       </c>
       <c r="C47" t="n">
-        <v>139</v>
+        <v>165</v>
       </c>
       <c r="D47" t="n">
-        <v>0.759562841530055</v>
+        <v>0.901639344262295</v>
       </c>
       <c r="E47" t="s">
         <v>16</v>
@@ -2586,10 +2574,10 @@
         <v>15</v>
       </c>
       <c r="C48" t="n">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="D48" t="n">
-        <v>0.901639344262295</v>
+        <v>0.923497267759563</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
@@ -2603,10 +2591,10 @@
         <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="D49" t="n">
-        <v>0.923497267759563</v>
+        <v>0.939890710382514</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -2620,10 +2608,10 @@
         <v>15</v>
       </c>
       <c r="C50" t="n">
-        <v>172</v>
+        <v>152</v>
       </c>
       <c r="D50" t="n">
-        <v>0.939890710382514</v>
+        <v>0.830601092896175</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
@@ -2637,10 +2625,10 @@
         <v>15</v>
       </c>
       <c r="C51" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D51" t="n">
-        <v>0.830601092896175</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
@@ -2654,10 +2642,10 @@
         <v>15</v>
       </c>
       <c r="C52" t="n">
-        <v>141</v>
+        <v>146</v>
       </c>
       <c r="D52" t="n">
-        <v>0.770491803278688</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -2671,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="C53" t="n">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="D53" t="n">
-        <v>0.797814207650273</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -2688,10 +2676,10 @@
         <v>15</v>
       </c>
       <c r="C54" t="n">
-        <v>153</v>
+        <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0.836065573770492</v>
+        <v>0.00546448087431694</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -2705,10 +2693,10 @@
         <v>15</v>
       </c>
       <c r="C55" t="n">
-        <v>1</v>
+        <v>179</v>
       </c>
       <c r="D55" t="n">
-        <v>0.00546448087431694</v>
+        <v>0.978142076502732</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
@@ -2722,10 +2710,10 @@
         <v>15</v>
       </c>
       <c r="C56" t="n">
-        <v>179</v>
+        <v>135</v>
       </c>
       <c r="D56" t="n">
-        <v>0.978142076502732</v>
+        <v>0.737704918032787</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -2739,10 +2727,10 @@
         <v>15</v>
       </c>
       <c r="C57" t="n">
-        <v>135</v>
+        <v>171</v>
       </c>
       <c r="D57" t="n">
-        <v>0.737704918032787</v>
+        <v>0.934426229508197</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -2773,10 +2761,10 @@
         <v>15</v>
       </c>
       <c r="C59" t="n">
-        <v>171</v>
+        <v>153</v>
       </c>
       <c r="D59" t="n">
-        <v>0.934426229508197</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -2790,10 +2778,10 @@
         <v>15</v>
       </c>
       <c r="C60" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D60" t="n">
-        <v>0.836065573770492</v>
+        <v>0.743169398907104</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -2807,10 +2795,10 @@
         <v>15</v>
       </c>
       <c r="C61" t="n">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D61" t="n">
-        <v>0.743169398907104</v>
+        <v>0.754098360655738</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -2824,10 +2812,10 @@
         <v>15</v>
       </c>
       <c r="C62" t="n">
-        <v>138</v>
+        <v>146</v>
       </c>
       <c r="D62" t="n">
-        <v>0.754098360655738</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -2841,10 +2829,10 @@
         <v>15</v>
       </c>
       <c r="C63" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="D63" t="n">
-        <v>0.797814207650273</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -2858,10 +2846,10 @@
         <v>15</v>
       </c>
       <c r="C64" t="n">
-        <v>177</v>
+        <v>158</v>
       </c>
       <c r="D64" t="n">
-        <v>0.967213114754098</v>
+        <v>0.863387978142076</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -2875,10 +2863,10 @@
         <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>158</v>
+        <v>152</v>
       </c>
       <c r="D65" t="n">
-        <v>0.863387978142076</v>
+        <v>0.830601092896175</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -2892,10 +2880,10 @@
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="D66" t="n">
-        <v>0.830601092896175</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -2909,10 +2897,10 @@
         <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>141</v>
+        <v>177</v>
       </c>
       <c r="D67" t="n">
-        <v>0.770491803278688</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
@@ -2926,10 +2914,10 @@
         <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>177</v>
+        <v>139</v>
       </c>
       <c r="D68" t="n">
-        <v>0.967213114754098</v>
+        <v>0.759562841530055</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
@@ -2943,10 +2931,10 @@
         <v>15</v>
       </c>
       <c r="C69" t="n">
-        <v>139</v>
+        <v>175</v>
       </c>
       <c r="D69" t="n">
-        <v>0.759562841530055</v>
+        <v>0.956284153005464</v>
       </c>
       <c r="E69" t="s">
         <v>16</v>
@@ -2960,10 +2948,10 @@
         <v>15</v>
       </c>
       <c r="C70" t="n">
-        <v>175</v>
+        <v>105</v>
       </c>
       <c r="D70" t="n">
-        <v>0.956284153005464</v>
+        <v>0.573770491803279</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
@@ -2977,10 +2965,10 @@
         <v>15</v>
       </c>
       <c r="C71" t="n">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D71" t="n">
-        <v>0.573770491803279</v>
+        <v>0.743169398907104</v>
       </c>
       <c r="E71" t="s">
         <v>16</v>
@@ -2994,10 +2982,10 @@
         <v>15</v>
       </c>
       <c r="C72" t="n">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="D72" t="n">
-        <v>0.743169398907104</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E72" t="s">
         <v>16</v>
@@ -3011,10 +2999,10 @@
         <v>15</v>
       </c>
       <c r="C73" t="n">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="D73" t="n">
-        <v>0.85792349726776</v>
+        <v>0.819672131147541</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
@@ -3028,10 +3016,10 @@
         <v>15</v>
       </c>
       <c r="C74" t="n">
-        <v>150</v>
+        <v>143</v>
       </c>
       <c r="D74" t="n">
-        <v>0.819672131147541</v>
+        <v>0.781420765027322</v>
       </c>
       <c r="E74" t="s">
         <v>16</v>
@@ -3045,10 +3033,10 @@
         <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>143</v>
+        <v>79</v>
       </c>
       <c r="D75" t="n">
-        <v>0.781420765027322</v>
+        <v>0.431693989071038</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
@@ -3062,10 +3050,10 @@
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>79</v>
+        <v>151</v>
       </c>
       <c r="D76" t="n">
-        <v>0.431693989071038</v>
+        <v>0.825136612021858</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
@@ -3079,10 +3067,10 @@
         <v>15</v>
       </c>
       <c r="C77" t="n">
-        <v>151</v>
+        <v>175</v>
       </c>
       <c r="D77" t="n">
-        <v>0.825136612021858</v>
+        <v>0.956284153005464</v>
       </c>
       <c r="E77" t="s">
         <v>16</v>
@@ -3096,10 +3084,10 @@
         <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="D78" t="n">
-        <v>0.956284153005464</v>
+        <v>0.983606557377049</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
@@ -3113,10 +3101,10 @@
         <v>15</v>
       </c>
       <c r="C79" t="n">
-        <v>180</v>
+        <v>154</v>
       </c>
       <c r="D79" t="n">
-        <v>0.983606557377049</v>
+        <v>0.841530054644809</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
@@ -3130,10 +3118,10 @@
         <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D80" t="n">
-        <v>0.841530054644809</v>
+        <v>0.825136612021858</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
@@ -3147,10 +3135,10 @@
         <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="D81" t="n">
-        <v>0.825136612021858</v>
+        <v>0.923497267759563</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
@@ -3164,10 +3152,10 @@
         <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>169</v>
+        <v>162</v>
       </c>
       <c r="D82" t="n">
-        <v>0.923497267759563</v>
+        <v>0.885245901639344</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -3181,10 +3169,10 @@
         <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="D83" t="n">
-        <v>0.885245901639344</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
@@ -3198,10 +3186,10 @@
         <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>173</v>
+        <v>166</v>
       </c>
       <c r="D84" t="n">
-        <v>0.945355191256831</v>
+        <v>0.907103825136612</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
@@ -3214,14 +3202,10 @@
       <c r="B85" t="s">
         <v>15</v>
       </c>
-      <c r="C85" t="n">
-        <v>166</v>
-      </c>
-      <c r="D85" t="n">
-        <v>0.907103825136612</v>
-      </c>
+      <c r="C85"/>
+      <c r="D85"/>
       <c r="E85" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="86">
@@ -3231,10 +3215,14 @@
       <c r="B86" t="s">
         <v>15</v>
       </c>
-      <c r="C86"/>
-      <c r="D86"/>
+      <c r="C86" t="n">
+        <v>162</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.885245901639344</v>
+      </c>
       <c r="E86" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="87">
@@ -3245,10 +3233,10 @@
         <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="D87" t="n">
-        <v>0.885245901639344</v>
+        <v>0.80327868852459</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
@@ -3262,10 +3250,10 @@
         <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="D88" t="n">
-        <v>0.80327868852459</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
@@ -3278,14 +3266,10 @@
       <c r="B89" t="s">
         <v>15</v>
       </c>
-      <c r="C89" t="n">
-        <v>157</v>
-      </c>
-      <c r="D89" t="n">
-        <v>0.85792349726776</v>
-      </c>
+      <c r="C89"/>
+      <c r="D89"/>
       <c r="E89" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="90">
@@ -3295,10 +3279,14 @@
       <c r="B90" t="s">
         <v>15</v>
       </c>
-      <c r="C90"/>
-      <c r="D90"/>
+      <c r="C90" t="n">
+        <v>160</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.87431693989071</v>
+      </c>
       <c r="E90" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="91">
@@ -3309,10 +3297,10 @@
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>160</v>
+        <v>172</v>
       </c>
       <c r="D91" t="n">
-        <v>0.87431693989071</v>
+        <v>0.939890710382514</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
@@ -3326,10 +3314,10 @@
         <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>172</v>
+        <v>139</v>
       </c>
       <c r="D92" t="n">
-        <v>0.939890710382514</v>
+        <v>0.759562841530055</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
@@ -3343,10 +3331,10 @@
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>141</v>
+        <v>149</v>
       </c>
       <c r="D93" t="n">
-        <v>0.770491803278688</v>
+        <v>0.814207650273224</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
@@ -3360,10 +3348,10 @@
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>167</v>
+        <v>139</v>
       </c>
       <c r="D94" t="n">
-        <v>0.912568306010929</v>
+        <v>0.759562841530055</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
@@ -3377,10 +3365,10 @@
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>139</v>
+        <v>134</v>
       </c>
       <c r="D95" t="n">
-        <v>0.759562841530055</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
@@ -3394,10 +3382,10 @@
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="D96" t="n">
-        <v>0.814207650273224</v>
+        <v>0.868852459016393</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
@@ -3411,10 +3399,10 @@
         <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D97" t="n">
-        <v>0.759562841530055</v>
+        <v>0.775956284153005</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
@@ -3428,10 +3416,10 @@
         <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>134</v>
+        <v>159</v>
       </c>
       <c r="D98" t="n">
-        <v>0.73224043715847</v>
+        <v>0.868852459016393</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
@@ -3445,10 +3433,10 @@
         <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>159</v>
+        <v>136</v>
       </c>
       <c r="D99" t="n">
-        <v>0.868852459016393</v>
+        <v>0.743169398907104</v>
       </c>
       <c r="E99" t="s">
         <v>16</v>
@@ -3462,10 +3450,10 @@
         <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>142</v>
+        <v>170</v>
       </c>
       <c r="D100" t="n">
-        <v>0.775956284153005</v>
+        <v>0.92896174863388</v>
       </c>
       <c r="E100" t="s">
         <v>16</v>
@@ -3479,10 +3467,10 @@
         <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>159</v>
+        <v>147</v>
       </c>
       <c r="D101" t="n">
-        <v>0.868852459016393</v>
+        <v>0.80327868852459</v>
       </c>
       <c r="E101" t="s">
         <v>16</v>
@@ -3496,10 +3484,10 @@
         <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>136</v>
+        <v>178</v>
       </c>
       <c r="D102" t="n">
-        <v>0.743169398907104</v>
+        <v>0.972677595628415</v>
       </c>
       <c r="E102" t="s">
         <v>16</v>
@@ -3513,10 +3501,10 @@
         <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="D103" t="n">
-        <v>0.918032786885246</v>
+        <v>0.934426229508197</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
@@ -3547,10 +3535,10 @@
         <v>15</v>
       </c>
       <c r="C105" t="n">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="D105" t="n">
-        <v>0.80327868852459</v>
+        <v>0.748633879781421</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
@@ -3564,10 +3552,10 @@
         <v>15</v>
       </c>
       <c r="C106" t="n">
-        <v>178</v>
+        <v>163</v>
       </c>
       <c r="D106" t="n">
-        <v>0.972677595628415</v>
+        <v>0.890710382513661</v>
       </c>
       <c r="E106" t="s">
         <v>16</v>
@@ -3581,10 +3569,10 @@
         <v>15</v>
       </c>
       <c r="C107" t="n">
-        <v>171</v>
+        <v>164</v>
       </c>
       <c r="D107" t="n">
-        <v>0.934426229508197</v>
+        <v>0.896174863387978</v>
       </c>
       <c r="E107" t="s">
         <v>16</v>
@@ -3598,10 +3586,10 @@
         <v>15</v>
       </c>
       <c r="C108" t="n">
-        <v>170</v>
+        <v>163</v>
       </c>
       <c r="D108" t="n">
-        <v>0.92896174863388</v>
+        <v>0.890710382513661</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
@@ -3615,10 +3603,10 @@
         <v>15</v>
       </c>
       <c r="C109" t="n">
-        <v>137</v>
+        <v>173</v>
       </c>
       <c r="D109" t="n">
-        <v>0.748633879781421</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E109" t="s">
         <v>16</v>
@@ -3632,10 +3620,10 @@
         <v>15</v>
       </c>
       <c r="C110" t="n">
-        <v>163</v>
+        <v>131</v>
       </c>
       <c r="D110" t="n">
-        <v>0.890710382513661</v>
+        <v>0.715846994535519</v>
       </c>
       <c r="E110" t="s">
         <v>16</v>
@@ -3649,10 +3637,10 @@
         <v>15</v>
       </c>
       <c r="C111" t="n">
-        <v>164</v>
+        <v>137</v>
       </c>
       <c r="D111" t="n">
-        <v>0.896174863387978</v>
+        <v>0.748633879781421</v>
       </c>
       <c r="E111" t="s">
         <v>16</v>
@@ -3666,10 +3654,10 @@
         <v>15</v>
       </c>
       <c r="C112" t="n">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D112" t="n">
-        <v>0.890710382513661</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E112" t="s">
         <v>16</v>
@@ -3683,10 +3671,10 @@
         <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>173</v>
+        <v>139</v>
       </c>
       <c r="D113" t="n">
-        <v>0.945355191256831</v>
+        <v>0.759562841530055</v>
       </c>
       <c r="E113" t="s">
         <v>16</v>
@@ -3700,10 +3688,10 @@
         <v>15</v>
       </c>
       <c r="C114" t="n">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D114" t="n">
-        <v>0.715846994535519</v>
+        <v>0.693989071038251</v>
       </c>
       <c r="E114" t="s">
         <v>16</v>
@@ -3717,10 +3705,10 @@
         <v>15</v>
       </c>
       <c r="C115" t="n">
-        <v>137</v>
+        <v>111</v>
       </c>
       <c r="D115" t="n">
-        <v>0.748633879781421</v>
+        <v>0.60655737704918</v>
       </c>
       <c r="E115" t="s">
         <v>16</v>
@@ -3734,10 +3722,10 @@
         <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>173</v>
+        <v>130</v>
       </c>
       <c r="D116" t="n">
-        <v>0.945355191256831</v>
+        <v>0.710382513661202</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
@@ -3751,10 +3739,10 @@
         <v>15</v>
       </c>
       <c r="C117" t="n">
-        <v>139</v>
+        <v>159</v>
       </c>
       <c r="D117" t="n">
-        <v>0.759562841530055</v>
+        <v>0.868852459016393</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
@@ -3768,10 +3756,10 @@
         <v>15</v>
       </c>
       <c r="C118" t="n">
-        <v>127</v>
+        <v>133</v>
       </c>
       <c r="D118" t="n">
-        <v>0.693989071038251</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
@@ -3785,10 +3773,10 @@
         <v>15</v>
       </c>
       <c r="C119" t="n">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="D119" t="n">
-        <v>0.60655737704918</v>
+        <v>0.628415300546448</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
@@ -3819,10 +3807,10 @@
         <v>15</v>
       </c>
       <c r="C121" t="n">
-        <v>159</v>
+        <v>150</v>
       </c>
       <c r="D121" t="n">
-        <v>0.868852459016393</v>
+        <v>0.819672131147541</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
@@ -3836,10 +3824,10 @@
         <v>15</v>
       </c>
       <c r="C122" t="n">
-        <v>133</v>
+        <v>138</v>
       </c>
       <c r="D122" t="n">
-        <v>0.726775956284153</v>
+        <v>0.754098360655738</v>
       </c>
       <c r="E122" t="s">
         <v>16</v>
@@ -3853,10 +3841,10 @@
         <v>15</v>
       </c>
       <c r="C123" t="n">
-        <v>115</v>
+        <v>124</v>
       </c>
       <c r="D123" t="n">
-        <v>0.628415300546448</v>
+        <v>0.6775956284153</v>
       </c>
       <c r="E123" t="s">
         <v>16</v>
@@ -3870,10 +3858,10 @@
         <v>15</v>
       </c>
       <c r="C124" t="n">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="D124" t="n">
-        <v>0.710382513661202</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
@@ -3887,10 +3875,10 @@
         <v>15</v>
       </c>
       <c r="C125" t="n">
-        <v>150</v>
+        <v>133</v>
       </c>
       <c r="D125" t="n">
-        <v>0.819672131147541</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
@@ -3904,10 +3892,10 @@
         <v>15</v>
       </c>
       <c r="C126" t="n">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="D126" t="n">
-        <v>0.754098360655738</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
@@ -3921,10 +3909,10 @@
         <v>15</v>
       </c>
       <c r="C127" t="n">
-        <v>124</v>
+        <v>169</v>
       </c>
       <c r="D127" t="n">
-        <v>0.6775956284153</v>
+        <v>0.923497267759563</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
@@ -3938,10 +3926,10 @@
         <v>15</v>
       </c>
       <c r="C128" t="n">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="D128" t="n">
-        <v>0.770491803278688</v>
+        <v>0.743169398907104</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -3955,10 +3943,10 @@
         <v>15</v>
       </c>
       <c r="C129" t="n">
-        <v>133</v>
+        <v>149</v>
       </c>
       <c r="D129" t="n">
-        <v>0.726775956284153</v>
+        <v>0.814207650273224</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -3972,10 +3960,10 @@
         <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="D130" t="n">
-        <v>0.73224043715847</v>
+        <v>0.775956284153005</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -3989,10 +3977,10 @@
         <v>15</v>
       </c>
       <c r="C131" t="n">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="D131" t="n">
-        <v>0.923497267759563</v>
+        <v>0.786885245901639</v>
       </c>
       <c r="E131" t="s">
         <v>16</v>
@@ -4006,10 +3994,10 @@
         <v>15</v>
       </c>
       <c r="C132" t="n">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="D132" t="n">
-        <v>0.743169398907104</v>
+        <v>0.617486338797814</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
@@ -4023,10 +4011,10 @@
         <v>15</v>
       </c>
       <c r="C133" t="n">
-        <v>149</v>
+        <v>137</v>
       </c>
       <c r="D133" t="n">
-        <v>0.814207650273224</v>
+        <v>0.748633879781421</v>
       </c>
       <c r="E133" t="s">
         <v>16</v>
@@ -4040,10 +4028,10 @@
         <v>15</v>
       </c>
       <c r="C134" t="n">
-        <v>142</v>
+        <v>157</v>
       </c>
       <c r="D134" t="n">
-        <v>0.775956284153005</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E134" t="s">
         <v>16</v>
@@ -4057,10 +4045,10 @@
         <v>15</v>
       </c>
       <c r="C135" t="n">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D135" t="n">
-        <v>0.786885245901639</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
@@ -4074,10 +4062,10 @@
         <v>15</v>
       </c>
       <c r="C136" t="n">
-        <v>113</v>
+        <v>172</v>
       </c>
       <c r="D136" t="n">
-        <v>0.617486338797814</v>
+        <v>0.939890710382514</v>
       </c>
       <c r="E136" t="s">
         <v>16</v>
@@ -4091,10 +4079,10 @@
         <v>15</v>
       </c>
       <c r="C137" t="n">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="D137" t="n">
-        <v>0.748633879781421</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E137" t="s">
         <v>16</v>
@@ -4108,10 +4096,10 @@
         <v>15</v>
       </c>
       <c r="C138" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="D138" t="n">
-        <v>0.85792349726776</v>
+        <v>0.80327868852459</v>
       </c>
       <c r="E138" t="s">
         <v>16</v>
@@ -4142,10 +4130,10 @@
         <v>15</v>
       </c>
       <c r="C140" t="n">
-        <v>172</v>
+        <v>146</v>
       </c>
       <c r="D140" t="n">
-        <v>0.939890710382514</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E140" t="s">
         <v>16</v>
@@ -4159,10 +4147,10 @@
         <v>15</v>
       </c>
       <c r="C141" t="n">
-        <v>146</v>
+        <v>133</v>
       </c>
       <c r="D141" t="n">
-        <v>0.797814207650273</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E141" t="s">
         <v>16</v>
@@ -4176,10 +4164,10 @@
         <v>15</v>
       </c>
       <c r="C142" t="n">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="D142" t="n">
-        <v>0.80327868852459</v>
+        <v>0.808743169398907</v>
       </c>
       <c r="E142" t="s">
         <v>16</v>
@@ -4193,10 +4181,10 @@
         <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="D143" t="n">
-        <v>0.73224043715847</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E143" t="s">
         <v>16</v>
@@ -4210,10 +4198,10 @@
         <v>15</v>
       </c>
       <c r="C144" t="n">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="D144" t="n">
-        <v>0.797814207650273</v>
+        <v>0.868852459016393</v>
       </c>
       <c r="E144" t="s">
         <v>16</v>
@@ -4227,10 +4215,10 @@
         <v>15</v>
       </c>
       <c r="C145" t="n">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="D145" t="n">
-        <v>0.726775956284153</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E145" t="s">
         <v>16</v>
@@ -4244,10 +4232,10 @@
         <v>15</v>
       </c>
       <c r="C146" t="n">
-        <v>148</v>
+        <v>164</v>
       </c>
       <c r="D146" t="n">
-        <v>0.808743169398907</v>
+        <v>0.896174863387978</v>
       </c>
       <c r="E146" t="s">
         <v>16</v>
@@ -4261,10 +4249,10 @@
         <v>15</v>
       </c>
       <c r="C147" t="n">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="D147" t="n">
-        <v>0.85792349726776</v>
+        <v>0.972677595628415</v>
       </c>
       <c r="E147" t="s">
         <v>16</v>
@@ -4278,10 +4266,10 @@
         <v>15</v>
       </c>
       <c r="C148" t="n">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="D148" t="n">
-        <v>0.868852459016393</v>
+        <v>0.786885245901639</v>
       </c>
       <c r="E148" t="s">
         <v>16</v>
@@ -4295,10 +4283,10 @@
         <v>15</v>
       </c>
       <c r="C149" t="n">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="D149" t="n">
-        <v>0.770491803278688</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E149" t="s">
         <v>16</v>
@@ -4312,10 +4300,10 @@
         <v>15</v>
       </c>
       <c r="C150" t="n">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="D150" t="n">
-        <v>0.896174863387978</v>
+        <v>0.978142076502732</v>
       </c>
       <c r="E150" t="s">
         <v>16</v>
@@ -4329,10 +4317,10 @@
         <v>15</v>
       </c>
       <c r="C151" t="n">
-        <v>178</v>
+        <v>149</v>
       </c>
       <c r="D151" t="n">
-        <v>0.972677595628415</v>
+        <v>0.814207650273224</v>
       </c>
       <c r="E151" t="s">
         <v>16</v>
@@ -4346,10 +4334,10 @@
         <v>15</v>
       </c>
       <c r="C152" t="n">
-        <v>144</v>
+        <v>175</v>
       </c>
       <c r="D152" t="n">
-        <v>0.786885245901639</v>
+        <v>0.956284153005464</v>
       </c>
       <c r="E152" t="s">
         <v>16</v>
@@ -4363,10 +4351,10 @@
         <v>15</v>
       </c>
       <c r="C153" t="n">
-        <v>153</v>
+        <v>136</v>
       </c>
       <c r="D153" t="n">
-        <v>0.836065573770492</v>
+        <v>0.743169398907104</v>
       </c>
       <c r="E153" t="s">
         <v>16</v>
@@ -4380,10 +4368,10 @@
         <v>15</v>
       </c>
       <c r="C154" t="n">
-        <v>179</v>
+        <v>144</v>
       </c>
       <c r="D154" t="n">
-        <v>0.978142076502732</v>
+        <v>0.786885245901639</v>
       </c>
       <c r="E154" t="s">
         <v>16</v>
@@ -4397,10 +4385,10 @@
         <v>15</v>
       </c>
       <c r="C155" t="n">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D155" t="n">
-        <v>0.814207650273224</v>
+        <v>0.80327868852459</v>
       </c>
       <c r="E155" t="s">
         <v>16</v>
@@ -4414,10 +4402,10 @@
         <v>15</v>
       </c>
       <c r="C156" t="n">
-        <v>175</v>
+        <v>138</v>
       </c>
       <c r="D156" t="n">
-        <v>0.956284153005464</v>
+        <v>0.754098360655738</v>
       </c>
       <c r="E156" t="s">
         <v>16</v>
@@ -4431,10 +4419,10 @@
         <v>15</v>
       </c>
       <c r="C157" t="n">
-        <v>136</v>
+        <v>175</v>
       </c>
       <c r="D157" t="n">
-        <v>0.743169398907104</v>
+        <v>0.956284153005464</v>
       </c>
       <c r="E157" t="s">
         <v>16</v>
@@ -4448,10 +4436,10 @@
         <v>15</v>
       </c>
       <c r="C158" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D158" t="n">
-        <v>0.786885245901639</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E158" t="s">
         <v>16</v>
@@ -4465,10 +4453,10 @@
         <v>15</v>
       </c>
       <c r="C159" t="n">
-        <v>147</v>
+        <v>133</v>
       </c>
       <c r="D159" t="n">
-        <v>0.80327868852459</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E159" t="s">
         <v>16</v>
@@ -4482,10 +4470,10 @@
         <v>15</v>
       </c>
       <c r="C160" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="D160" t="n">
-        <v>0.754098360655738</v>
+        <v>0.770491803278688</v>
       </c>
       <c r="E160" t="s">
         <v>16</v>
@@ -4499,10 +4487,10 @@
         <v>15</v>
       </c>
       <c r="C161" t="n">
-        <v>175</v>
+        <v>134</v>
       </c>
       <c r="D161" t="n">
-        <v>0.956284153005464</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E161" t="s">
         <v>16</v>
@@ -4516,10 +4504,10 @@
         <v>15</v>
       </c>
       <c r="C162" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="D162" t="n">
-        <v>0.770491803278688</v>
+        <v>0.710382513661202</v>
       </c>
       <c r="E162" t="s">
         <v>16</v>
@@ -4533,10 +4521,10 @@
         <v>15</v>
       </c>
       <c r="C163" t="n">
-        <v>133</v>
+        <v>164</v>
       </c>
       <c r="D163" t="n">
-        <v>0.726775956284153</v>
+        <v>0.896174863387978</v>
       </c>
       <c r="E163" t="s">
         <v>16</v>
@@ -4550,10 +4538,10 @@
         <v>15</v>
       </c>
       <c r="C164" t="n">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="D164" t="n">
-        <v>0.770491803278688</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E164" t="s">
         <v>16</v>
@@ -4567,10 +4555,10 @@
         <v>15</v>
       </c>
       <c r="C165" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D165" t="n">
-        <v>0.73224043715847</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E165" t="s">
         <v>16</v>
@@ -4584,10 +4572,10 @@
         <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>130</v>
+        <v>163</v>
       </c>
       <c r="D166" t="n">
-        <v>0.710382513661202</v>
+        <v>0.890710382513661</v>
       </c>
       <c r="E166" t="s">
         <v>16</v>
@@ -4601,10 +4589,10 @@
         <v>15</v>
       </c>
       <c r="C167" t="n">
-        <v>164</v>
+        <v>147</v>
       </c>
       <c r="D167" t="n">
-        <v>0.896174863387978</v>
+        <v>0.80327868852459</v>
       </c>
       <c r="E167" t="s">
         <v>16</v>
@@ -4618,10 +4606,10 @@
         <v>15</v>
       </c>
       <c r="C168" t="n">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D168" t="n">
-        <v>0.85792349726776</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E168" t="s">
         <v>16</v>
@@ -4635,10 +4623,10 @@
         <v>15</v>
       </c>
       <c r="C169" t="n">
-        <v>153</v>
+        <v>168</v>
       </c>
       <c r="D169" t="n">
-        <v>0.836065573770492</v>
+        <v>0.918032786885246</v>
       </c>
       <c r="E169" t="s">
         <v>16</v>
@@ -4652,10 +4640,10 @@
         <v>15</v>
       </c>
       <c r="C170" t="n">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="D170" t="n">
-        <v>0.890710382513661</v>
+        <v>0.972677595628415</v>
       </c>
       <c r="E170" t="s">
         <v>16</v>
@@ -4669,10 +4657,10 @@
         <v>15</v>
       </c>
       <c r="C171" t="n">
-        <v>147</v>
+        <v>173</v>
       </c>
       <c r="D171" t="n">
-        <v>0.80327868852459</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E171" t="s">
         <v>16</v>
@@ -4686,10 +4674,10 @@
         <v>15</v>
       </c>
       <c r="C172" t="n">
-        <v>153</v>
+        <v>173</v>
       </c>
       <c r="D172" t="n">
-        <v>0.836065573770492</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E172" t="s">
         <v>16</v>
@@ -4703,10 +4691,10 @@
         <v>15</v>
       </c>
       <c r="C173" t="n">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="D173" t="n">
-        <v>0.918032786885246</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E173" t="s">
         <v>16</v>
@@ -4720,10 +4708,10 @@
         <v>15</v>
       </c>
       <c r="C174" t="n">
-        <v>178</v>
+        <v>164</v>
       </c>
       <c r="D174" t="n">
-        <v>0.972677595628415</v>
+        <v>0.896174863387978</v>
       </c>
       <c r="E174" t="s">
         <v>16</v>
@@ -4737,10 +4725,10 @@
         <v>15</v>
       </c>
       <c r="C175" t="n">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="D175" t="n">
-        <v>0.945355191256831</v>
+        <v>0.846994535519126</v>
       </c>
       <c r="E175" t="s">
         <v>16</v>
@@ -4754,10 +4742,10 @@
         <v>15</v>
       </c>
       <c r="C176" t="n">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="D176" t="n">
-        <v>0.945355191256831</v>
+        <v>0.830601092896175</v>
       </c>
       <c r="E176" t="s">
         <v>16</v>
@@ -4771,10 +4759,10 @@
         <v>15</v>
       </c>
       <c r="C177" t="n">
-        <v>177</v>
+        <v>153</v>
       </c>
       <c r="D177" t="n">
-        <v>0.967213114754098</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E177" t="s">
         <v>16</v>
@@ -4805,10 +4793,10 @@
         <v>15</v>
       </c>
       <c r="C179" t="n">
-        <v>155</v>
+        <v>164</v>
       </c>
       <c r="D179" t="n">
-        <v>0.846994535519126</v>
+        <v>0.896174863387978</v>
       </c>
       <c r="E179" t="s">
         <v>16</v>
@@ -4822,10 +4810,10 @@
         <v>15</v>
       </c>
       <c r="C180" t="n">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="D180" t="n">
-        <v>0.830601092896175</v>
+        <v>0.87431693989071</v>
       </c>
       <c r="E180" t="s">
         <v>16</v>
@@ -4839,10 +4827,10 @@
         <v>15</v>
       </c>
       <c r="C181" t="n">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D181" t="n">
-        <v>0.836065573770492</v>
+        <v>0.830601092896175</v>
       </c>
       <c r="E181" t="s">
         <v>16</v>
@@ -4856,10 +4844,10 @@
         <v>15</v>
       </c>
       <c r="C182" t="n">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="D182" t="n">
-        <v>0.896174863387978</v>
+        <v>0.85792349726776</v>
       </c>
       <c r="E182" t="s">
         <v>16</v>
@@ -4873,10 +4861,10 @@
         <v>15</v>
       </c>
       <c r="C183" t="n">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D183" t="n">
-        <v>0.896174863387978</v>
+        <v>0.901639344262295</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
@@ -4890,10 +4878,10 @@
         <v>15</v>
       </c>
       <c r="C184" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="D184" t="n">
-        <v>0.87431693989071</v>
+        <v>0.92896174863388</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
@@ -4907,10 +4895,10 @@
         <v>15</v>
       </c>
       <c r="C185" t="n">
-        <v>152</v>
+        <v>177</v>
       </c>
       <c r="D185" t="n">
-        <v>0.830601092896175</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E185" t="s">
         <v>16</v>
@@ -4924,10 +4912,10 @@
         <v>15</v>
       </c>
       <c r="C186" t="n">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="D186" t="n">
-        <v>0.85792349726776</v>
+        <v>0.92896174863388</v>
       </c>
       <c r="E186" t="s">
         <v>16</v>
@@ -4941,10 +4929,10 @@
         <v>15</v>
       </c>
       <c r="C187" t="n">
-        <v>165</v>
+        <v>134</v>
       </c>
       <c r="D187" t="n">
-        <v>0.901639344262295</v>
+        <v>0.73224043715847</v>
       </c>
       <c r="E187" t="s">
         <v>16</v>
@@ -4958,10 +4946,10 @@
         <v>15</v>
       </c>
       <c r="C188" t="n">
-        <v>170</v>
+        <v>133</v>
       </c>
       <c r="D188" t="n">
-        <v>0.92896174863388</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E188" t="s">
         <v>16</v>
@@ -4974,14 +4962,10 @@
       <c r="B189" t="s">
         <v>15</v>
       </c>
-      <c r="C189" t="n">
-        <v>177</v>
-      </c>
-      <c r="D189" t="n">
-        <v>0.967213114754098</v>
-      </c>
+      <c r="C189"/>
+      <c r="D189"/>
       <c r="E189" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="190">
@@ -4992,10 +4976,10 @@
         <v>15</v>
       </c>
       <c r="C190" t="n">
-        <v>170</v>
+        <v>128</v>
       </c>
       <c r="D190" t="n">
-        <v>0.92896174863388</v>
+        <v>0.699453551912568</v>
       </c>
       <c r="E190" t="s">
         <v>16</v>
@@ -5009,10 +4993,10 @@
         <v>15</v>
       </c>
       <c r="C191" t="n">
-        <v>134</v>
+        <v>153</v>
       </c>
       <c r="D191" t="n">
-        <v>0.73224043715847</v>
+        <v>0.836065573770492</v>
       </c>
       <c r="E191" t="s">
         <v>16</v>
@@ -5026,10 +5010,10 @@
         <v>15</v>
       </c>
       <c r="C192" t="n">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="D192" t="n">
-        <v>0.726775956284153</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E192" t="s">
         <v>16</v>
@@ -5042,10 +5026,14 @@
       <c r="B193" t="s">
         <v>15</v>
       </c>
-      <c r="C193"/>
-      <c r="D193"/>
+      <c r="C193" t="n">
+        <v>143</v>
+      </c>
+      <c r="D193" t="n">
+        <v>0.781420765027322</v>
+      </c>
       <c r="E193" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="194">
@@ -5056,10 +5044,10 @@
         <v>15</v>
       </c>
       <c r="C194" t="n">
-        <v>128</v>
+        <v>133</v>
       </c>
       <c r="D194" t="n">
-        <v>0.699453551912568</v>
+        <v>0.726775956284153</v>
       </c>
       <c r="E194" t="s">
         <v>16</v>
@@ -5073,10 +5061,10 @@
         <v>15</v>
       </c>
       <c r="C195" t="n">
-        <v>153</v>
+        <v>91</v>
       </c>
       <c r="D195" t="n">
-        <v>0.836065573770492</v>
+        <v>0.497267759562842</v>
       </c>
       <c r="E195" t="s">
         <v>16</v>
@@ -5090,10 +5078,10 @@
         <v>15</v>
       </c>
       <c r="C196" t="n">
-        <v>146</v>
+        <v>126</v>
       </c>
       <c r="D196" t="n">
-        <v>0.797814207650273</v>
+        <v>0.688524590163934</v>
       </c>
       <c r="E196" t="s">
         <v>16</v>
@@ -5107,10 +5095,10 @@
         <v>15</v>
       </c>
       <c r="C197" t="n">
-        <v>143</v>
+        <v>171</v>
       </c>
       <c r="D197" t="n">
-        <v>0.781420765027322</v>
+        <v>0.934426229508197</v>
       </c>
       <c r="E197" t="s">
         <v>16</v>
@@ -5124,10 +5112,10 @@
         <v>15</v>
       </c>
       <c r="C198" t="n">
-        <v>133</v>
+        <v>173</v>
       </c>
       <c r="D198" t="n">
-        <v>0.726775956284153</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E198" t="s">
         <v>16</v>
@@ -5141,10 +5129,10 @@
         <v>15</v>
       </c>
       <c r="C199" t="n">
-        <v>91</v>
+        <v>132</v>
       </c>
       <c r="D199" t="n">
-        <v>0.497267759562842</v>
+        <v>0.721311475409836</v>
       </c>
       <c r="E199" t="s">
         <v>16</v>
@@ -5158,10 +5146,10 @@
         <v>15</v>
       </c>
       <c r="C200" t="n">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="D200" t="n">
-        <v>0.688524590163934</v>
+        <v>0.66120218579235</v>
       </c>
       <c r="E200" t="s">
         <v>16</v>
@@ -5175,10 +5163,10 @@
         <v>15</v>
       </c>
       <c r="C201" t="n">
-        <v>171</v>
+        <v>142</v>
       </c>
       <c r="D201" t="n">
-        <v>0.934426229508197</v>
+        <v>0.775956284153005</v>
       </c>
       <c r="E201" t="s">
         <v>16</v>
@@ -5192,10 +5180,10 @@
         <v>15</v>
       </c>
       <c r="C202" t="n">
-        <v>173</v>
+        <v>154</v>
       </c>
       <c r="D202" t="n">
-        <v>0.945355191256831</v>
+        <v>0.841530054644809</v>
       </c>
       <c r="E202" t="s">
         <v>16</v>
@@ -5209,10 +5197,10 @@
         <v>15</v>
       </c>
       <c r="C203" t="n">
-        <v>132</v>
+        <v>162</v>
       </c>
       <c r="D203" t="n">
-        <v>0.721311475409836</v>
+        <v>0.885245901639344</v>
       </c>
       <c r="E203" t="s">
         <v>16</v>
@@ -5226,10 +5214,10 @@
         <v>15</v>
       </c>
       <c r="C204" t="n">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="D204" t="n">
-        <v>0.66120218579235</v>
+        <v>0.852459016393443</v>
       </c>
       <c r="E204" t="s">
         <v>16</v>
@@ -5243,10 +5231,10 @@
         <v>15</v>
       </c>
       <c r="C205" t="n">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="D205" t="n">
-        <v>0.775956284153005</v>
+        <v>0.846994535519126</v>
       </c>
       <c r="E205" t="s">
         <v>16</v>
@@ -5260,10 +5248,10 @@
         <v>15</v>
       </c>
       <c r="C206" t="n">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="D206" t="n">
-        <v>0.841530054644809</v>
+        <v>0.797814207650273</v>
       </c>
       <c r="E206" t="s">
         <v>16</v>
@@ -5277,10 +5265,10 @@
         <v>15</v>
       </c>
       <c r="C207" t="n">
-        <v>162</v>
+        <v>180</v>
       </c>
       <c r="D207" t="n">
-        <v>0.885245901639344</v>
+        <v>0.983606557377049</v>
       </c>
       <c r="E207" t="s">
         <v>16</v>
@@ -5294,10 +5282,10 @@
         <v>15</v>
       </c>
       <c r="C208" t="n">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D208" t="n">
-        <v>0.852459016393443</v>
+        <v>0.934426229508197</v>
       </c>
       <c r="E208" t="s">
         <v>16</v>
@@ -5311,10 +5299,10 @@
         <v>15</v>
       </c>
       <c r="C209" t="n">
-        <v>155</v>
+        <v>177</v>
       </c>
       <c r="D209" t="n">
-        <v>0.846994535519126</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E209" t="s">
         <v>16</v>
@@ -5328,10 +5316,10 @@
         <v>15</v>
       </c>
       <c r="C210" t="n">
-        <v>146</v>
+        <v>177</v>
       </c>
       <c r="D210" t="n">
-        <v>0.797814207650273</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E210" t="s">
         <v>16</v>
@@ -5345,10 +5333,10 @@
         <v>15</v>
       </c>
       <c r="C211" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D211" t="n">
-        <v>0.983606557377049</v>
+        <v>0.961748633879781</v>
       </c>
       <c r="E211" t="s">
         <v>16</v>
@@ -5362,10 +5350,10 @@
         <v>15</v>
       </c>
       <c r="C212" t="n">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D212" t="n">
-        <v>0.934426229508197</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E212" t="s">
         <v>16</v>
@@ -5379,10 +5367,10 @@
         <v>15</v>
       </c>
       <c r="C213" t="n">
-        <v>177</v>
+        <v>173</v>
       </c>
       <c r="D213" t="n">
-        <v>0.967213114754098</v>
+        <v>0.945355191256831</v>
       </c>
       <c r="E213" t="s">
         <v>16</v>
@@ -5396,10 +5384,10 @@
         <v>15</v>
       </c>
       <c r="C214" t="n">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="D214" t="n">
-        <v>0.967213114754098</v>
+        <v>0.972677595628415</v>
       </c>
       <c r="E214" t="s">
         <v>16</v>
@@ -5413,10 +5401,10 @@
         <v>15</v>
       </c>
       <c r="C215" t="n">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="D215" t="n">
-        <v>0.961748633879781</v>
+        <v>0.967213114754098</v>
       </c>
       <c r="E215" t="s">
         <v>16</v>
@@ -5429,14 +5417,10 @@
       <c r="B216" t="s">
         <v>15</v>
       </c>
-      <c r="C216" t="n">
-        <v>177</v>
-      </c>
-      <c r="D216" t="n">
-        <v>0.967213114754098</v>
-      </c>
+      <c r="C216"/>
+      <c r="D216"/>
       <c r="E216" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="217">
@@ -5447,10 +5431,10 @@
         <v>15</v>
       </c>
       <c r="C217" t="n">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D217" t="n">
-        <v>0.945355191256831</v>
+        <v>0.923497267759563</v>
       </c>
       <c r="E217" t="s">
         <v>16</v>
@@ -5464,10 +5448,10 @@
         <v>15</v>
       </c>
       <c r="C218" t="n">
-        <v>178</v>
+        <v>120</v>
       </c>
       <c r="D218" t="n">
-        <v>0.972677595628415</v>
+        <v>0.655737704918033</v>
       </c>
       <c r="E218" t="s">
         <v>16</v>
@@ -5481,10 +5465,10 @@
         <v>15</v>
       </c>
       <c r="C219" t="n">
-        <v>177</v>
+        <v>52</v>
       </c>
       <c r="D219" t="n">
-        <v>0.967213114754098</v>
+        <v>0.284153005464481</v>
       </c>
       <c r="E219" t="s">
         <v>16</v>
@@ -5511,10 +5495,10 @@
         <v>15</v>
       </c>
       <c r="C221" t="n">
-        <v>169</v>
+        <v>72</v>
       </c>
       <c r="D221" t="n">
-        <v>0.923497267759563</v>
+        <v>0.39344262295082</v>
       </c>
       <c r="E221" t="s">
         <v>16</v>
@@ -5528,10 +5512,10 @@
         <v>15</v>
       </c>
       <c r="C222" t="n">
-        <v>120</v>
+        <v>8</v>
       </c>
       <c r="D222" t="n">
-        <v>0.655737704918033</v>
+        <v>0.0437158469945355</v>
       </c>
       <c r="E222" t="s">
         <v>16</v>
@@ -5545,10 +5529,10 @@
         <v>15</v>
       </c>
       <c r="C223" t="n">
-        <v>52</v>
+        <v>1</v>
       </c>
       <c r="D223" t="n">
-        <v>0.284153005464481</v>
+        <v>0.00546448087431694</v>
       </c>
       <c r="E223" t="s">
         <v>16</v>
@@ -5561,10 +5545,14 @@
       <c r="B224" t="s">
         <v>15</v>
       </c>
-      <c r="C224"/>
-      <c r="D224"/>
+      <c r="C224" t="n">
+        <v>133</v>
+      </c>
+      <c r="D224" t="n">
+        <v>0.726775956284153</v>
+      </c>
       <c r="E224" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="225">
@@ -5575,10 +5563,10 @@
         <v>15</v>
       </c>
       <c r="C225" t="n">
-        <v>72</v>
+        <v>55</v>
       </c>
       <c r="D225" t="n">
-        <v>0.39344262295082</v>
+        <v>0.300546448087432</v>
       </c>
       <c r="E225" t="s">
         <v>16</v>
@@ -5592,10 +5580,10 @@
         <v>15</v>
       </c>
       <c r="C226" t="n">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="D226" t="n">
-        <v>0.0437158469945355</v>
+        <v>0.163934426229508</v>
       </c>
       <c r="E226" t="s">
         <v>16</v>
@@ -5609,10 +5597,10 @@
         <v>15</v>
       </c>
       <c r="C227" t="n">
-        <v>1</v>
+        <v>38</v>
       </c>
       <c r="D227" t="n">
-        <v>0.00546448087431694</v>
+        <v>0.207650273224044</v>
       </c>
       <c r="E227" t="s">
         <v>16</v>
@@ -5626,10 +5614,10 @@
         <v>15</v>
       </c>
       <c r="C228" t="n">
-        <v>133</v>
+        <v>14</v>
       </c>
       <c r="D228" t="n">
-        <v>0.726775956284153</v>
+        <v>0.0765027322404372</v>
       </c>
       <c r="E228" t="s">
         <v>16</v>
@@ -5643,10 +5631,10 @@
         <v>15</v>
       </c>
       <c r="C229" t="n">
-        <v>55</v>
+        <v>158</v>
       </c>
       <c r="D229" t="n">
-        <v>0.300546448087432</v>
+        <v>0.863387978142076</v>
       </c>
       <c r="E229" t="s">
         <v>16</v>
@@ -5660,10 +5648,10 @@
         <v>15</v>
       </c>
       <c r="C230" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
       <c r="D230" t="n">
-        <v>0.163934426229508</v>
+        <v>0.00546448087431694</v>
       </c>
       <c r="E230" t="s">
         <v>16</v>
@@ -5677,10 +5665,10 @@
         <v>15</v>
       </c>
       <c r="C231" t="n">
-        <v>38</v>
+        <v>74</v>
       </c>
       <c r="D231" t="n">
-        <v>0.207650273224044</v>
+        <v>0.404371584699454</v>
       </c>
       <c r="E231" t="s">
         <v>16</v>
@@ -5694,10 +5682,10 @@
         <v>15</v>
       </c>
       <c r="C232" t="n">
-        <v>14</v>
+        <v>38</v>
       </c>
       <c r="D232" t="n">
-        <v>0.0765027322404372</v>
+        <v>0.207650273224044</v>
       </c>
       <c r="E232" t="s">
         <v>16</v>
@@ -5711,10 +5699,10 @@
         <v>15</v>
       </c>
       <c r="C233" t="n">
-        <v>158</v>
+        <v>12</v>
       </c>
       <c r="D233" t="n">
-        <v>0.863387978142076</v>
+        <v>0.0655737704918033</v>
       </c>
       <c r="E233" t="s">
         <v>16</v>
@@ -5727,14 +5715,10 @@
       <c r="B234" t="s">
         <v>15</v>
       </c>
-      <c r="C234" t="n">
-        <v>1</v>
-      </c>
-      <c r="D234" t="n">
-        <v>0.00546448087431694</v>
-      </c>
+      <c r="C234"/>
+      <c r="D234"/>
       <c r="E234" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="235">
@@ -5745,10 +5729,10 @@
         <v>15</v>
       </c>
       <c r="C235" t="n">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="D235" t="n">
-        <v>0.404371584699454</v>
+        <v>0.431693989071038</v>
       </c>
       <c r="E235" t="s">
         <v>16</v>
@@ -5761,14 +5745,10 @@
       <c r="B236" t="s">
         <v>15</v>
       </c>
-      <c r="C236" t="n">
-        <v>38</v>
-      </c>
-      <c r="D236" t="n">
-        <v>0.207650273224044</v>
-      </c>
+      <c r="C236"/>
+      <c r="D236"/>
       <c r="E236" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="237">
@@ -5779,10 +5759,10 @@
         <v>15</v>
       </c>
       <c r="C237" t="n">
-        <v>12</v>
+        <v>120</v>
       </c>
       <c r="D237" t="n">
-        <v>0.0655737704918033</v>
+        <v>0.655737704918033</v>
       </c>
       <c r="E237" t="s">
         <v>16</v>
@@ -5795,10 +5775,14 @@
       <c r="B238" t="s">
         <v>15</v>
       </c>
-      <c r="C238"/>
-      <c r="D238"/>
+      <c r="C238" t="n">
+        <v>134</v>
+      </c>
+      <c r="D238" t="n">
+        <v>0.73224043715847</v>
+      </c>
       <c r="E238" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="239">
@@ -5809,10 +5793,10 @@
         <v>15</v>
       </c>
       <c r="C239" t="n">
-        <v>79</v>
+        <v>176</v>
       </c>
       <c r="D239" t="n">
-        <v>0.431693989071038</v>
+        <v>0.961748633879781</v>
       </c>
       <c r="E239" t="s">
         <v>16</v>
@@ -5825,10 +5809,14 @@
       <c r="B240" t="s">
         <v>15</v>
       </c>
-      <c r="C240"/>
-      <c r="D240"/>
+      <c r="C240" t="n">
+        <v>30</v>
+      </c>
+      <c r="D240" t="n">
+        <v>0.163934426229508</v>
+      </c>
       <c r="E240" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="241">
@@ -5839,10 +5827,10 @@
         <v>15</v>
       </c>
       <c r="C241" t="n">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="D241" t="n">
-        <v>0.655737704918033</v>
+        <v>0.956284153005464</v>
       </c>
       <c r="E241" t="s">
         <v>16</v>
@@ -5856,10 +5844,10 @@
         <v>15</v>
       </c>
       <c r="C242" t="n">
-        <v>134</v>
+        <v>148</v>
       </c>
       <c r="D242" t="n">
-        <v>0.73224043715847</v>
+        <v>0.808743169398907</v>
       </c>
       <c r="E242" t="s">
         <v>16</v>
@@ -5873,10 +5861,10 @@
         <v>15</v>
       </c>
       <c r="C243" t="n">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D243" t="n">
-        <v>0.961748633879781</v>
+        <v>0.950819672131147</v>
       </c>
       <c r="E243" t="s">
         <v>16</v>
@@ -5890,10 +5878,10 @@
         <v>15</v>
       </c>
       <c r="C244" t="n">
-        <v>30</v>
+        <v>123</v>
       </c>
       <c r="D244" t="n">
-        <v>0.163934426229508</v>
+        <v>0.672131147540984</v>
       </c>
       <c r="E244" t="s">
         <v>16</v>
@@ -5907,10 +5895,10 @@
         <v>15</v>
       </c>
       <c r="C245" t="n">
-        <v>175</v>
+        <v>158</v>
       </c>
       <c r="D245" t="n">
-        <v>0.956284153005464</v>
+        <v>0.863387978142076</v>
       </c>
       <c r="E245" t="s">
         <v>16</v>
@@ -5924,10 +5912,10 @@
         <v>15</v>
       </c>
       <c r="C246" t="n">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D246" t="n">
-        <v>0.808743169398907</v>
+        <v>0.830601092896175</v>
       </c>
       <c r="E246" t="s">
         <v>16</v>
@@ -5941,10 +5929,10 @@
         <v>15</v>
       </c>
       <c r="C247" t="n">
-        <v>174</v>
+        <v>149</v>
       </c>
       <c r="D247" t="n">
-        <v>0.950819672131147</v>
+        <v>0.814207650273224</v>
       </c>
       <c r="E247" t="s">
         <v>16</v>
@@ -5957,14 +5945,10 @@
       <c r="B248" t="s">
         <v>15</v>
       </c>
-      <c r="C248" t="n">
-        <v>123</v>
-      </c>
-      <c r="D248" t="n">
-        <v>0.672131147540984</v>
-      </c>
+      <c r="C248"/>
+      <c r="D248"/>
       <c r="E248" t="s">
-        <v>16</v>
+        <v>41</v>
       </c>
     </row>
     <row r="249">
@@ -5975,10 +5959,10 @@
         <v>15</v>
       </c>
       <c r="C249" t="n">
-        <v>158</v>
+        <v>2</v>
       </c>
       <c r="D249" t="n">
-        <v>0.863387978142076</v>
+        <v>0.0109289617486339</v>
       </c>
       <c r="E249" t="s">
         <v>16</v>
@@ -5992,10 +5976,10 @@
         <v>15</v>
       </c>
       <c r="C250" t="n">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="D250" t="n">
-        <v>0.830601092896175</v>
+        <v>0.781420765027322</v>
       </c>
       <c r="E250" t="s">
         <v>16</v>
@@ -6009,10 +5993,10 @@
         <v>15</v>
       </c>
       <c r="C251" t="n">
-        <v>149</v>
+        <v>94</v>
       </c>
       <c r="D251" t="n">
-        <v>0.814207650273224</v>
+        <v>0.513661202185792</v>
       </c>
       <c r="E251" t="s">
         <v>16</v>
@@ -6025,10 +6009,14 @@
       <c r="B252" t="s">
         <v>15</v>
       </c>
-      <c r="C252"/>
-      <c r="D252"/>
+      <c r="C252" t="n">
+        <v>106</v>
+      </c>
+      <c r="D252" t="n">
+        <v>0.579234972677596</v>
+      </c>
       <c r="E252" t="s">
-        <v>41</v>
+        <v>16</v>
       </c>
     </row>
     <row r="253">
@@ -6039,10 +6027,10 @@
         <v>15</v>
       </c>
       <c r="C253" t="n">
-        <v>2</v>
+        <v>132</v>
       </c>
       <c r="D253" t="n">
-        <v>0.0109289617486339</v>
+        <v>0.721311475409836</v>
       </c>
       <c r="E253" t="s">
         <v>16</v>
@@ -6056,10 +6044,10 @@
         <v>15</v>
       </c>
       <c r="C254" t="n">
-        <v>143</v>
+        <v>8</v>
       </c>
       <c r="D254" t="n">
-        <v>0.781420765027322</v>
+        <v>0.0437158469945355</v>
       </c>
       <c r="E254" t="s">
         <v>16</v>
@@ -6073,10 +6061,10 @@
         <v>15</v>
       </c>
       <c r="C255" t="n">
-        <v>94</v>
+        <v>30</v>
       </c>
       <c r="D255" t="n">
-        <v>0.513661202185792</v>
+        <v>0.163934426229508</v>
       </c>
       <c r="E255" t="s">
         <v>16</v>
@@ -6090,10 +6078,10 @@
         <v>15</v>
       </c>
       <c r="C256" t="n">
-        <v>106</v>
+        <v>2</v>
       </c>
       <c r="D256" t="n">
-        <v>0.579234972677596</v>
+        <v>0.0109289617486339</v>
       </c>
       <c r="E256" t="s">
         <v>16</v>
@@ -6107,10 +6095,10 @@
         <v>15</v>
       </c>
       <c r="C257" t="n">
-        <v>132</v>
+        <v>68</v>
       </c>
       <c r="D257" t="n">
-        <v>0.721311475409836</v>
+        <v>0.371584699453552</v>
       </c>
       <c r="E257" t="s">
         <v>16</v>
@@ -6124,10 +6112,10 @@
         <v>15</v>
       </c>
       <c r="C258" t="n">
-        <v>8</v>
+        <v>98</v>
       </c>
       <c r="D258" t="n">
-        <v>0.0437158469945355</v>
+        <v>0.53551912568306</v>
       </c>
       <c r="E258" t="s">
         <v>16</v>
@@ -6141,80 +6129,12 @@
         <v>15</v>
       </c>
       <c r="C259" t="n">
-        <v>30</v>
+        <v>99</v>
       </c>
       <c r="D259" t="n">
-        <v>0.163934426229508</v>
+        <v>0.540983606557377</v>
       </c>
       <c r="E259" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="260">
-      <c r="A260" t="s">
-        <v>275</v>
-      </c>
-      <c r="B260" t="s">
-        <v>15</v>
-      </c>
-      <c r="C260" t="n">
-        <v>2</v>
-      </c>
-      <c r="D260" t="n">
-        <v>0.0109289617486339</v>
-      </c>
-      <c r="E260" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="261">
-      <c r="A261" t="s">
-        <v>276</v>
-      </c>
-      <c r="B261" t="s">
-        <v>15</v>
-      </c>
-      <c r="C261" t="n">
-        <v>68</v>
-      </c>
-      <c r="D261" t="n">
-        <v>0.371584699453552</v>
-      </c>
-      <c r="E261" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="262">
-      <c r="A262" t="s">
-        <v>277</v>
-      </c>
-      <c r="B262" t="s">
-        <v>15</v>
-      </c>
-      <c r="C262" t="n">
-        <v>98</v>
-      </c>
-      <c r="D262" t="n">
-        <v>0.53551912568306</v>
-      </c>
-      <c r="E262" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" t="s">
-        <v>278</v>
-      </c>
-      <c r="B263" t="s">
-        <v>15</v>
-      </c>
-      <c r="C263" t="n">
-        <v>99</v>
-      </c>
-      <c r="D263" t="n">
-        <v>0.540983606557377</v>
-      </c>
-      <c r="E263" t="s">
         <v>16</v>
       </c>
     </row>
@@ -6231,13 +6151,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="B1" t="s">
         <v>10</v>
       </c>
       <c r="C1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="D1" t="s">
         <v>12</v>
@@ -6248,16 +6168,16 @@
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
       </c>
       <c r="C2" t="n">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="D2" t="n">
-        <v>0.996031746031746</v>
+        <v>0.995967741935484</v>
       </c>
       <c r="E2" t="s">
         <v>16</v>
@@ -6265,16 +6185,16 @@
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="B3" t="s">
         <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D3" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E3" t="s">
         <v>16</v>
@@ -6282,16 +6202,16 @@
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
       <c r="B4" t="s">
         <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D4" t="n">
-        <v>0.976190476190476</v>
+        <v>0.975806451612903</v>
       </c>
       <c r="E4" t="s">
         <v>16</v>
@@ -6299,16 +6219,16 @@
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
       <c r="B5" t="s">
         <v>15</v>
       </c>
       <c r="C5" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D5" t="n">
-        <v>0.968253968253968</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E5" t="s">
         <v>16</v>
@@ -6316,16 +6236,16 @@
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="B6" t="s">
         <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D6" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E6" t="s">
         <v>16</v>
@@ -6333,16 +6253,16 @@
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
       </c>
       <c r="C7" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D7" t="n">
-        <v>0.944444444444444</v>
+        <v>0.943548387096774</v>
       </c>
       <c r="E7" t="s">
         <v>16</v>
@@ -6350,16 +6270,16 @@
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
       <c r="B8" t="s">
         <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D8" t="n">
-        <v>0.900793650793651</v>
+        <v>0.899193548387097</v>
       </c>
       <c r="E8" t="s">
         <v>16</v>
@@ -6367,16 +6287,16 @@
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="B9" t="s">
         <v>15</v>
       </c>
       <c r="C9" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D9" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E9" t="s">
         <v>16</v>
@@ -6384,16 +6304,16 @@
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="B10" t="s">
         <v>15</v>
       </c>
       <c r="C10" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D10" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E10" t="s">
         <v>16</v>
@@ -6401,16 +6321,16 @@
     </row>
     <row r="11">
       <c r="A11" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="B11" t="s">
         <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D11" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E11" t="s">
         <v>16</v>
@@ -6418,16 +6338,16 @@
     </row>
     <row r="12">
       <c r="A12" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D12" t="n">
-        <v>0.968253968253968</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E12" t="s">
         <v>16</v>
@@ -6435,16 +6355,16 @@
     </row>
     <row r="13">
       <c r="A13" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="B13" t="s">
         <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D13" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E13" t="s">
         <v>16</v>
@@ -6452,16 +6372,16 @@
     </row>
     <row r="14">
       <c r="A14" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="B14" t="s">
         <v>15</v>
       </c>
       <c r="C14" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D14" t="n">
-        <v>0.968253968253968</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E14" t="s">
         <v>16</v>
@@ -6469,16 +6389,16 @@
     </row>
     <row r="15">
       <c r="A15" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B15" t="s">
         <v>15</v>
       </c>
       <c r="C15" t="n">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="D15" t="n">
-        <v>0.801587301587302</v>
+        <v>0.798387096774194</v>
       </c>
       <c r="E15" t="s">
         <v>16</v>
@@ -6486,16 +6406,16 @@
     </row>
     <row r="16">
       <c r="A16" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="B16" t="s">
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D16" t="n">
-        <v>0.944444444444444</v>
+        <v>0.943548387096774</v>
       </c>
       <c r="E16" t="s">
         <v>16</v>
@@ -6503,16 +6423,16 @@
     </row>
     <row r="17">
       <c r="A17" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="B17" t="s">
         <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D17" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E17" t="s">
         <v>16</v>
@@ -6520,16 +6440,16 @@
     </row>
     <row r="18">
       <c r="A18" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="B18" t="s">
         <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D18" t="n">
-        <v>0.920634920634921</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E18" t="s">
         <v>16</v>
@@ -6537,16 +6457,16 @@
     </row>
     <row r="19">
       <c r="A19" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="B19" t="s">
         <v>15</v>
       </c>
       <c r="C19" t="n">
-        <v>184</v>
+        <v>238</v>
       </c>
       <c r="D19" t="n">
-        <v>0.73015873015873</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E19" t="s">
         <v>16</v>
@@ -6554,16 +6474,16 @@
     </row>
     <row r="20">
       <c r="A20" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="B20" t="s">
         <v>15</v>
       </c>
       <c r="C20" t="n">
-        <v>242</v>
+        <v>180</v>
       </c>
       <c r="D20" t="n">
-        <v>0.96031746031746</v>
+        <v>0.725806451612903</v>
       </c>
       <c r="E20" t="s">
         <v>16</v>
@@ -6571,16 +6491,16 @@
     </row>
     <row r="21">
       <c r="A21" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="n">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D21" t="n">
-        <v>0.80952380952381</v>
+        <v>0.806451612903226</v>
       </c>
       <c r="E21" t="s">
         <v>16</v>
@@ -6588,16 +6508,16 @@
     </row>
     <row r="22">
       <c r="A22" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="B22" t="s">
         <v>15</v>
       </c>
       <c r="C22" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D22" t="n">
-        <v>0.944444444444444</v>
+        <v>0.943548387096774</v>
       </c>
       <c r="E22" t="s">
         <v>16</v>
@@ -6605,16 +6525,16 @@
     </row>
     <row r="23">
       <c r="A23" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="B23" t="s">
         <v>15</v>
       </c>
       <c r="C23" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D23" t="n">
-        <v>0.956349206349206</v>
+        <v>0.955645161290323</v>
       </c>
       <c r="E23" t="s">
         <v>16</v>
@@ -6622,16 +6542,16 @@
     </row>
     <row r="24">
       <c r="A24" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="B24" t="s">
         <v>15</v>
       </c>
       <c r="C24" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D24" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E24" t="s">
         <v>16</v>
@@ -6639,16 +6559,16 @@
     </row>
     <row r="25">
       <c r="A25" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="B25" t="s">
         <v>15</v>
       </c>
       <c r="C25" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D25" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E25" t="s">
         <v>16</v>
@@ -6656,16 +6576,16 @@
     </row>
     <row r="26">
       <c r="A26" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s">
         <v>15</v>
       </c>
       <c r="C26" t="n">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="D26" t="n">
-        <v>0.785714285714286</v>
+        <v>0.786290322580645</v>
       </c>
       <c r="E26" t="s">
         <v>16</v>
@@ -6673,16 +6593,16 @@
     </row>
     <row r="27">
       <c r="A27" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="B27" t="s">
         <v>15</v>
       </c>
       <c r="C27" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D27" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E27" t="s">
         <v>16</v>
@@ -6690,16 +6610,16 @@
     </row>
     <row r="28">
       <c r="A28" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="B28" t="s">
         <v>15</v>
       </c>
       <c r="C28" t="n">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="D28" t="n">
-        <v>0.968253968253968</v>
+        <v>0.967741935483871</v>
       </c>
       <c r="E28" t="s">
         <v>16</v>
@@ -6707,16 +6627,16 @@
     </row>
     <row r="29">
       <c r="A29" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="B29" t="s">
         <v>15</v>
       </c>
       <c r="C29" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D29" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E29" t="s">
         <v>16</v>
@@ -6724,16 +6644,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="B30" t="s">
         <v>15</v>
       </c>
       <c r="C30" t="n">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="D30" t="n">
-        <v>0.694444444444444</v>
+        <v>0.689516129032258</v>
       </c>
       <c r="E30" t="s">
         <v>16</v>
@@ -6741,16 +6661,16 @@
     </row>
     <row r="31">
       <c r="A31" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="B31" t="s">
         <v>15</v>
       </c>
       <c r="C31" t="n">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D31" t="n">
-        <v>0.964285714285714</v>
+        <v>0.963709677419355</v>
       </c>
       <c r="E31" t="s">
         <v>16</v>
@@ -6758,16 +6678,16 @@
     </row>
     <row r="32">
       <c r="A32" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="B32" t="s">
         <v>15</v>
       </c>
       <c r="C32" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D32" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E32" t="s">
         <v>16</v>
@@ -6775,16 +6695,16 @@
     </row>
     <row r="33">
       <c r="A33" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="B33" t="s">
         <v>15</v>
       </c>
       <c r="C33" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D33" t="n">
-        <v>0.956349206349206</v>
+        <v>0.955645161290323</v>
       </c>
       <c r="E33" t="s">
         <v>16</v>
@@ -6792,16 +6712,16 @@
     </row>
     <row r="34">
       <c r="A34" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s">
         <v>15</v>
       </c>
       <c r="C34" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D34" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E34" t="s">
         <v>16</v>
@@ -6809,16 +6729,16 @@
     </row>
     <row r="35">
       <c r="A35" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="B35" t="s">
         <v>15</v>
       </c>
       <c r="C35" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D35" t="n">
-        <v>0.956349206349206</v>
+        <v>0.955645161290323</v>
       </c>
       <c r="E35" t="s">
         <v>16</v>
@@ -6826,16 +6746,16 @@
     </row>
     <row r="36">
       <c r="A36" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="B36" t="s">
         <v>15</v>
       </c>
       <c r="C36" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D36" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E36" t="s">
         <v>16</v>
@@ -6843,16 +6763,16 @@
     </row>
     <row r="37">
       <c r="A37" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="B37" t="s">
         <v>15</v>
       </c>
       <c r="C37" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D37" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E37" t="s">
         <v>16</v>
@@ -6860,16 +6780,16 @@
     </row>
     <row r="38">
       <c r="A38" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="B38" t="s">
         <v>15</v>
       </c>
       <c r="C38" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D38" t="n">
-        <v>0.916666666666667</v>
+        <v>0.915322580645161</v>
       </c>
       <c r="E38" t="s">
         <v>16</v>
@@ -6877,16 +6797,16 @@
     </row>
     <row r="39">
       <c r="A39" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="B39" t="s">
         <v>15</v>
       </c>
       <c r="C39" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D39" t="n">
-        <v>0.932539682539683</v>
+        <v>0.931451612903226</v>
       </c>
       <c r="E39" t="s">
         <v>16</v>
@@ -6894,16 +6814,16 @@
     </row>
     <row r="40">
       <c r="A40" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B40" t="s">
         <v>15</v>
       </c>
       <c r="C40" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D40" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E40" t="s">
         <v>16</v>
@@ -6911,16 +6831,16 @@
     </row>
     <row r="41">
       <c r="A41" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="B41" t="s">
         <v>15</v>
       </c>
       <c r="C41" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D41" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E41" t="s">
         <v>16</v>
@@ -6928,16 +6848,16 @@
     </row>
     <row r="42">
       <c r="A42" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="B42" t="s">
         <v>15</v>
       </c>
       <c r="C42" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D42" t="n">
-        <v>0.956349206349206</v>
+        <v>0.955645161290323</v>
       </c>
       <c r="E42" t="s">
         <v>16</v>
@@ -6945,16 +6865,16 @@
     </row>
     <row r="43">
       <c r="A43" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="B43" t="s">
         <v>15</v>
       </c>
       <c r="C43" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D43" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E43" t="s">
         <v>16</v>
@@ -6962,16 +6882,16 @@
     </row>
     <row r="44">
       <c r="A44" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="B44" t="s">
         <v>15</v>
       </c>
       <c r="C44" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D44" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E44" t="s">
         <v>16</v>
@@ -6979,16 +6899,16 @@
     </row>
     <row r="45">
       <c r="A45" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="B45" t="s">
         <v>15</v>
       </c>
       <c r="C45" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D45" t="n">
-        <v>0.944444444444444</v>
+        <v>0.943548387096774</v>
       </c>
       <c r="E45" t="s">
         <v>16</v>
@@ -6996,16 +6916,16 @@
     </row>
     <row r="46">
       <c r="A46" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="B46" t="s">
         <v>15</v>
       </c>
       <c r="C46" t="n">
-        <v>180</v>
+        <v>176</v>
       </c>
       <c r="D46" t="n">
-        <v>0.714285714285714</v>
+        <v>0.709677419354839</v>
       </c>
       <c r="E46" t="s">
         <v>16</v>
@@ -7013,16 +6933,16 @@
     </row>
     <row r="47">
       <c r="A47" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="B47" t="s">
         <v>15</v>
       </c>
       <c r="C47" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D47" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E47" t="s">
         <v>16</v>
@@ -7030,16 +6950,16 @@
     </row>
     <row r="48">
       <c r="A48" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="B48" t="s">
         <v>15</v>
       </c>
       <c r="C48" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D48" t="n">
-        <v>0.928571428571429</v>
+        <v>0.92741935483871</v>
       </c>
       <c r="E48" t="s">
         <v>16</v>
@@ -7047,16 +6967,16 @@
     </row>
     <row r="49">
       <c r="A49" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B49" t="s">
         <v>15</v>
       </c>
       <c r="C49" t="n">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D49" t="n">
-        <v>0.952380952380952</v>
+        <v>0.951612903225806</v>
       </c>
       <c r="E49" t="s">
         <v>16</v>
@@ -7064,16 +6984,16 @@
     </row>
     <row r="50">
       <c r="A50" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="B50" t="s">
         <v>15</v>
       </c>
       <c r="C50" t="n">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="D50" t="n">
-        <v>0.96031746031746</v>
+        <v>0.959677419354839</v>
       </c>
       <c r="E50" t="s">
         <v>16</v>
@@ -7081,16 +7001,16 @@
     </row>
     <row r="51">
       <c r="A51" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="B51" t="s">
         <v>15</v>
       </c>
       <c r="C51" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D51" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E51" t="s">
         <v>16</v>
@@ -7098,16 +7018,16 @@
     </row>
     <row r="52">
       <c r="A52" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="B52" t="s">
         <v>15</v>
       </c>
       <c r="C52" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D52" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E52" t="s">
         <v>16</v>
@@ -7115,16 +7035,16 @@
     </row>
     <row r="53">
       <c r="A53" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="B53" t="s">
         <v>15</v>
       </c>
       <c r="C53" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D53" t="n">
-        <v>0.924603174603175</v>
+        <v>0.923387096774194</v>
       </c>
       <c r="E53" t="s">
         <v>16</v>
@@ -7132,16 +7052,16 @@
     </row>
     <row r="54">
       <c r="A54" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="B54" t="s">
         <v>15</v>
       </c>
       <c r="C54" t="n">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="D54" t="n">
-        <v>0.944444444444444</v>
+        <v>0.943548387096774</v>
       </c>
       <c r="E54" t="s">
         <v>16</v>
@@ -7149,16 +7069,16 @@
     </row>
     <row r="55">
       <c r="A55" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="B55" t="s">
         <v>15</v>
       </c>
       <c r="C55" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D55" t="n">
-        <v>0.932539682539683</v>
+        <v>0.931451612903226</v>
       </c>
       <c r="E55" t="s">
         <v>16</v>
@@ -7166,16 +7086,16 @@
     </row>
     <row r="56">
       <c r="A56" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="B56" t="s">
         <v>15</v>
       </c>
       <c r="C56" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D56" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E56" t="s">
         <v>16</v>
@@ -7183,16 +7103,16 @@
     </row>
     <row r="57">
       <c r="A57" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="B57" t="s">
         <v>15</v>
       </c>
       <c r="C57" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D57" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E57" t="s">
         <v>16</v>
@@ -7200,16 +7120,16 @@
     </row>
     <row r="58">
       <c r="A58" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="B58" t="s">
         <v>15</v>
       </c>
       <c r="C58" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D58" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E58" t="s">
         <v>16</v>
@@ -7217,16 +7137,16 @@
     </row>
     <row r="59">
       <c r="A59" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="B59" t="s">
         <v>15</v>
       </c>
       <c r="C59" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D59" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E59" t="s">
         <v>16</v>
@@ -7234,16 +7154,16 @@
     </row>
     <row r="60">
       <c r="A60" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="B60" t="s">
         <v>15</v>
       </c>
       <c r="C60" t="n">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="D60" t="n">
-        <v>0.837301587301587</v>
+        <v>0.834677419354839</v>
       </c>
       <c r="E60" t="s">
         <v>16</v>
@@ -7251,16 +7171,16 @@
     </row>
     <row r="61">
       <c r="A61" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="B61" t="s">
         <v>15</v>
       </c>
       <c r="C61" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D61" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E61" t="s">
         <v>16</v>
@@ -7268,16 +7188,16 @@
     </row>
     <row r="62">
       <c r="A62" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="B62" t="s">
         <v>15</v>
       </c>
       <c r="C62" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D62" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E62" t="s">
         <v>16</v>
@@ -7285,16 +7205,16 @@
     </row>
     <row r="63">
       <c r="A63" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="B63" t="s">
         <v>15</v>
       </c>
       <c r="C63" t="n">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="D63" t="n">
-        <v>0.948412698412698</v>
+        <v>0.94758064516129</v>
       </c>
       <c r="E63" t="s">
         <v>16</v>
@@ -7302,16 +7222,16 @@
     </row>
     <row r="64">
       <c r="A64" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="B64" t="s">
         <v>15</v>
       </c>
       <c r="C64" t="n">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="D64" t="n">
-        <v>0.920634920634921</v>
+        <v>0.919354838709677</v>
       </c>
       <c r="E64" t="s">
         <v>16</v>
@@ -7319,16 +7239,16 @@
     </row>
     <row r="65">
       <c r="A65" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="B65" t="s">
         <v>15</v>
       </c>
       <c r="C65" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D65" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E65" t="s">
         <v>16</v>
@@ -7336,16 +7256,16 @@
     </row>
     <row r="66">
       <c r="A66" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="B66" t="s">
         <v>15</v>
       </c>
       <c r="C66" t="n">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D66" t="n">
-        <v>0.670634920634921</v>
+        <v>0.665322580645161</v>
       </c>
       <c r="E66" t="s">
         <v>16</v>
@@ -7353,16 +7273,16 @@
     </row>
     <row r="67">
       <c r="A67" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="B67" t="s">
         <v>15</v>
       </c>
       <c r="C67" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D67" t="n">
-        <v>0.884920634920635</v>
+        <v>0.883064516129032</v>
       </c>
       <c r="E67" t="s">
         <v>16</v>
@@ -7370,16 +7290,16 @@
     </row>
     <row r="68">
       <c r="A68" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="B68" t="s">
         <v>15</v>
       </c>
       <c r="C68" t="n">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="D68" t="n">
-        <v>0.785714285714286</v>
+        <v>0.782258064516129</v>
       </c>
       <c r="E68" t="s">
         <v>16</v>
@@ -7387,16 +7307,16 @@
     </row>
     <row r="69">
       <c r="A69" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="B69" t="s">
         <v>15</v>
       </c>
       <c r="C69" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D69" t="n">
-        <v>0.928571428571429</v>
+        <v>0.92741935483871</v>
       </c>
       <c r="E69" t="s">
         <v>16</v>
@@ -7404,16 +7324,16 @@
     </row>
     <row r="70">
       <c r="A70" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="B70" t="s">
         <v>15</v>
       </c>
       <c r="C70" t="n">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D70" t="n">
-        <v>0.928571428571429</v>
+        <v>0.92741935483871</v>
       </c>
       <c r="E70" t="s">
         <v>16</v>
@@ -7421,16 +7341,16 @@
     </row>
     <row r="71">
       <c r="A71" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="B71" t="s">
         <v>15</v>
       </c>
       <c r="C71" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D71" t="n">
-        <v>0.924603174603175</v>
+        <v>0.923387096774194</v>
       </c>
       <c r="E71" t="s">
         <v>16</v>
@@ -7438,16 +7358,16 @@
     </row>
     <row r="72">
       <c r="A72" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="B72" t="s">
         <v>15</v>
       </c>
       <c r="C72" t="n">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D72" t="n">
-        <v>0.797619047619048</v>
+        <v>0.794354838709677</v>
       </c>
       <c r="E72" t="s">
         <v>16</v>
@@ -7455,16 +7375,16 @@
     </row>
     <row r="73">
       <c r="A73" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="B73" t="s">
         <v>15</v>
       </c>
       <c r="C73" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D73" t="n">
-        <v>0.908730158730159</v>
+        <v>0.907258064516129</v>
       </c>
       <c r="E73" t="s">
         <v>16</v>
@@ -7472,16 +7392,16 @@
     </row>
     <row r="74">
       <c r="A74" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="B74" t="s">
         <v>15</v>
       </c>
       <c r="C74" t="n">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="D74" t="n">
-        <v>0.932539682539683</v>
+        <v>0.931451612903226</v>
       </c>
       <c r="E74" t="s">
         <v>16</v>
@@ -7489,16 +7409,16 @@
     </row>
     <row r="75">
       <c r="A75" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="B75" t="s">
         <v>15</v>
       </c>
       <c r="C75" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D75" t="n">
-        <v>0.892857142857143</v>
+        <v>0.891129032258065</v>
       </c>
       <c r="E75" t="s">
         <v>16</v>
@@ -7506,16 +7426,16 @@
     </row>
     <row r="76">
       <c r="A76" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="B76" t="s">
         <v>15</v>
       </c>
       <c r="C76" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D76" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E76" t="s">
         <v>16</v>
@@ -7523,16 +7443,16 @@
     </row>
     <row r="77">
       <c r="A77" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="B77" t="s">
         <v>15</v>
       </c>
       <c r="C77" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D77" t="n">
-        <v>0.924603174603175</v>
+        <v>0.923387096774194</v>
       </c>
       <c r="E77" t="s">
         <v>16</v>
@@ -7540,16 +7460,16 @@
     </row>
     <row r="78">
       <c r="A78" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="B78" t="s">
         <v>15</v>
       </c>
       <c r="C78" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D78" t="n">
-        <v>0.912698412698413</v>
+        <v>0.911290322580645</v>
       </c>
       <c r="E78" t="s">
         <v>16</v>
@@ -7557,16 +7477,16 @@
     </row>
     <row r="79">
       <c r="A79" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="B79" t="s">
         <v>15</v>
       </c>
       <c r="C79" t="n">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="D79" t="n">
-        <v>0.924603174603175</v>
+        <v>0.923387096774194</v>
       </c>
       <c r="E79" t="s">
         <v>16</v>
@@ -7574,16 +7494,16 @@
     </row>
     <row r="80">
       <c r="A80" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="B80" t="s">
         <v>15</v>
       </c>
       <c r="C80" t="n">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D80" t="n">
-        <v>0.908730158730159</v>
+        <v>0.907258064516129</v>
       </c>
       <c r="E80" t="s">
         <v>16</v>
@@ -7591,16 +7511,16 @@
     </row>
     <row r="81">
       <c r="A81" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="B81" t="s">
         <v>15</v>
       </c>
       <c r="C81" t="n">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D81" t="n">
-        <v>0.892857142857143</v>
+        <v>0.891129032258065</v>
       </c>
       <c r="E81" t="s">
         <v>16</v>
@@ -7608,16 +7528,16 @@
     </row>
     <row r="82">
       <c r="A82" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="B82" t="s">
         <v>15</v>
       </c>
       <c r="C82" t="n">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="D82" t="n">
-        <v>0.896825396825397</v>
+        <v>0.895161290322581</v>
       </c>
       <c r="E82" t="s">
         <v>16</v>
@@ -7625,16 +7545,16 @@
     </row>
     <row r="83">
       <c r="A83" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="B83" t="s">
         <v>15</v>
       </c>
       <c r="C83" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D83" t="n">
-        <v>0.904761904761905</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="E83" t="s">
         <v>16</v>
@@ -7642,16 +7562,16 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="B84" t="s">
         <v>15</v>
       </c>
       <c r="C84" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D84" t="n">
-        <v>0.880952380952381</v>
+        <v>0.879032258064516</v>
       </c>
       <c r="E84" t="s">
         <v>16</v>
@@ -7659,16 +7579,16 @@
     </row>
     <row r="85">
       <c r="A85" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="B85" t="s">
         <v>15</v>
       </c>
       <c r="C85" t="n">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="D85" t="n">
-        <v>0.853174603174603</v>
+        <v>0.850806451612903</v>
       </c>
       <c r="E85" t="s">
         <v>16</v>
@@ -7676,16 +7596,16 @@
     </row>
     <row r="86">
       <c r="A86" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="B86" t="s">
         <v>15</v>
       </c>
       <c r="C86" t="n">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="D86" t="n">
-        <v>0.936507936507937</v>
+        <v>0.935483870967742</v>
       </c>
       <c r="E86" t="s">
         <v>16</v>
@@ -7693,16 +7613,16 @@
     </row>
     <row r="87">
       <c r="A87" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="B87" t="s">
         <v>15</v>
       </c>
       <c r="C87" t="n">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="D87" t="n">
-        <v>0.884920634920635</v>
+        <v>0.887096774193548</v>
       </c>
       <c r="E87" t="s">
         <v>16</v>
@@ -7710,16 +7630,16 @@
     </row>
     <row r="88">
       <c r="A88" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="B88" t="s">
         <v>15</v>
       </c>
       <c r="C88" t="n">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D88" t="n">
-        <v>0.94047619047619</v>
+        <v>0.939516129032258</v>
       </c>
       <c r="E88" t="s">
         <v>16</v>
@@ -7727,16 +7647,16 @@
     </row>
     <row r="89">
       <c r="A89" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="B89" t="s">
         <v>15</v>
       </c>
       <c r="C89" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D89" t="n">
-        <v>0.900793650793651</v>
+        <v>0.899193548387097</v>
       </c>
       <c r="E89" t="s">
         <v>16</v>
@@ -7744,16 +7664,16 @@
     </row>
     <row r="90">
       <c r="A90" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="B90" t="s">
         <v>15</v>
       </c>
       <c r="C90" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D90" t="n">
-        <v>0.888888888888889</v>
+        <v>0.887096774193548</v>
       </c>
       <c r="E90" t="s">
         <v>16</v>
@@ -7761,16 +7681,16 @@
     </row>
     <row r="91">
       <c r="A91" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="B91" t="s">
         <v>15</v>
       </c>
       <c r="C91" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D91" t="n">
-        <v>0.912698412698413</v>
+        <v>0.911290322580645</v>
       </c>
       <c r="E91" t="s">
         <v>16</v>
@@ -7778,16 +7698,16 @@
     </row>
     <row r="92">
       <c r="A92" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="B92" t="s">
         <v>15</v>
       </c>
       <c r="C92" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D92" t="n">
-        <v>0.904761904761905</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="E92" t="s">
         <v>16</v>
@@ -7795,16 +7715,16 @@
     </row>
     <row r="93">
       <c r="A93" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="B93" t="s">
         <v>15</v>
       </c>
       <c r="C93" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D93" t="n">
-        <v>0.904761904761905</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="E93" t="s">
         <v>16</v>
@@ -7812,16 +7732,16 @@
     </row>
     <row r="94">
       <c r="A94" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="B94" t="s">
         <v>15</v>
       </c>
       <c r="C94" t="n">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="D94" t="n">
-        <v>0.912698412698413</v>
+        <v>0.911290322580645</v>
       </c>
       <c r="E94" t="s">
         <v>16</v>
@@ -7829,16 +7749,16 @@
     </row>
     <row r="95">
       <c r="A95" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="B95" t="s">
         <v>15</v>
       </c>
       <c r="C95" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D95" t="n">
-        <v>0.825396825396825</v>
+        <v>0.82258064516129</v>
       </c>
       <c r="E95" t="s">
         <v>16</v>
@@ -7846,16 +7766,16 @@
     </row>
     <row r="96">
       <c r="A96" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="B96" t="s">
         <v>15</v>
       </c>
       <c r="C96" t="n">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="D96" t="n">
-        <v>0.956349206349206</v>
+        <v>0.955645161290323</v>
       </c>
       <c r="E96" t="s">
         <v>16</v>
@@ -7863,16 +7783,16 @@
     </row>
     <row r="97">
       <c r="A97" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="B97" t="s">
         <v>15</v>
       </c>
       <c r="C97" t="n">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="D97" t="n">
-        <v>0.880952380952381</v>
+        <v>0.879032258064516</v>
       </c>
       <c r="E97" t="s">
         <v>16</v>
@@ -7880,16 +7800,16 @@
     </row>
     <row r="98">
       <c r="A98" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="B98" t="s">
         <v>15</v>
       </c>
       <c r="C98" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D98" t="n">
-        <v>0.884920634920635</v>
+        <v>0.883064516129032</v>
       </c>
       <c r="E98" t="s">
         <v>16</v>
@@ -7897,16 +7817,16 @@
     </row>
     <row r="99">
       <c r="A99" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="B99" t="s">
         <v>15</v>
       </c>
       <c r="C99" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D99" t="n">
-        <v>0.900793650793651</v>
+        <v>0.899193548387097</v>
       </c>
       <c r="E99" t="s">
         <v>16</v>
@@ -7914,16 +7834,16 @@
     </row>
     <row r="100">
       <c r="A100" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="B100" t="s">
         <v>15</v>
       </c>
       <c r="C100" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D100" t="n">
-        <v>0.916666666666667</v>
+        <v>0.915322580645161</v>
       </c>
       <c r="E100" t="s">
         <v>16</v>
@@ -7931,16 +7851,16 @@
     </row>
     <row r="101">
       <c r="A101" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="B101" t="s">
         <v>15</v>
       </c>
       <c r="C101" t="n">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D101" t="n">
-        <v>0.916666666666667</v>
+        <v>0.915322580645161</v>
       </c>
       <c r="E101" t="s">
         <v>16</v>
@@ -7948,16 +7868,16 @@
     </row>
     <row r="102">
       <c r="A102" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="B102" t="s">
         <v>15</v>
       </c>
       <c r="C102" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D102" t="n">
-        <v>0.876984126984127</v>
+        <v>0.875</v>
       </c>
       <c r="E102" t="s">
         <v>16</v>
@@ -7965,16 +7885,16 @@
     </row>
     <row r="103">
       <c r="A103" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="B103" t="s">
         <v>15</v>
       </c>
       <c r="C103" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D103" t="n">
-        <v>0.884920634920635</v>
+        <v>0.883064516129032</v>
       </c>
       <c r="E103" t="s">
         <v>16</v>
@@ -7982,16 +7902,16 @@
     </row>
     <row r="104">
       <c r="A104" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="B104" t="s">
         <v>15</v>
       </c>
       <c r="C104" t="n">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D104" t="n">
-        <v>0.904761904761905</v>
+        <v>0.903225806451613</v>
       </c>
       <c r="E104" t="s">
         <v>16</v>
@@ -7999,16 +7919,16 @@
     </row>
     <row r="105">
       <c r="A105" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="B105" t="s">
         <v>15</v>
       </c>
       <c r="C105" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D105" t="n">
-        <v>0.900793650793651</v>
+        <v>0.899193548387097</v>
       </c>
       <c r="E105" t="s">
         <v>16</v>
@@ -8016,16 +7936,16 @@
     </row>
     <row r="106">
       <c r="A106" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="B106" t="s">
         <v>15</v>
       </c>
       <c r="C106" t="n">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="D106" t="n">
-        <v>0.900793650793651</v>
+        <v>0.899193548387097</v>
       </c>
       <c r="E106" t="s">
         <v>16</v>
@@ -8033,16 +7953,16 @@
     </row>
     <row r="107">
       <c r="A107" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="B107" t="s">
         <v>15</v>
       </c>
       <c r="C107" t="n">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D107" t="n">
-        <v>0.821428571428571</v>
+        <v>0.818548387096774</v>
       </c>
       <c r="E107" t="s">
         <v>16</v>
@@ -8050,16 +7970,16 @@
     </row>
     <row r="108">
       <c r="A108" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="B108" t="s">
         <v>15</v>
       </c>
       <c r="C108" t="n">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D108" t="n">
-        <v>0.857142857142857</v>
+        <v>0.854838709677419</v>
       </c>
       <c r="E108" t="s">
         <v>16</v>
@@ -8067,16 +7987,16 @@
     </row>
     <row r="109">
       <c r="A109" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="B109" t="s">
         <v>15</v>
       </c>
       <c r="C109" t="n">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="D109" t="n">
-        <v>0.833333333333333</v>
+        <v>0.911290322580645</v>
       </c>
       <c r="E109" t="s">
         <v>16</v>
@@ -8084,16 +8004,16 @@
     </row>
     <row r="110">
       <c r="A110" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="B110" t="s">
         <v>15</v>
       </c>
       <c r="C110" t="n">
-        <v>230</v>
+        <v>206</v>
       </c>
       <c r="D110" t="n">
-        <v>0.912698412698413</v>
+        <v>0.830645161290323</v>
       </c>
       <c r="E110" t="s">
         <v>16</v>
@@ -8101,16 +8021,16 @@
     </row>
     <row r="111">
       <c r="A111" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="B111" t="s">
         <v>15</v>
       </c>
       <c r="C111" t="n">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="D111" t="n">
-        <v>0.888888888888889</v>
+        <v>0.887096774193548</v>
       </c>
       <c r="E111" t="s">
         <v>16</v>
@@ -8118,16 +8038,16 @@
     </row>
     <row r="112">
       <c r="A112" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="B112" t="s">
         <v>15</v>
       </c>
       <c r="C112" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D112" t="n">
-        <v>0.884920634920635</v>
+        <v>0.883064516129032</v>
       </c>
       <c r="E112" t="s">
         <v>16</v>
@@ -8135,16 +8055,16 @@
     </row>
     <row r="113">
       <c r="A113" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="B113" t="s">
         <v>15</v>
       </c>
       <c r="C113" t="n">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="D113" t="n">
-        <v>0.884920634920635</v>
+        <v>0.883064516129032</v>
       </c>
       <c r="E113" t="s">
         <v>16</v>
@@ -8152,16 +8072,16 @@
     </row>
     <row r="114">
       <c r="A114" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="B114" t="s">
         <v>15</v>
       </c>
       <c r="C114" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D114" t="n">
-        <v>0.876984126984127</v>
+        <v>0.875</v>
       </c>
       <c r="E114" t="s">
         <v>16</v>
@@ -8169,16 +8089,16 @@
     </row>
     <row r="115">
       <c r="A115" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="B115" t="s">
         <v>15</v>
       </c>
       <c r="C115" t="n">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="D115" t="n">
-        <v>0.857142857142857</v>
+        <v>0.858870967741935</v>
       </c>
       <c r="E115" t="s">
         <v>16</v>
@@ -8186,16 +8106,16 @@
     </row>
     <row r="116">
       <c r="A116" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="B116" t="s">
         <v>15</v>
       </c>
       <c r="C116" t="n">
-        <v>220</v>
+        <v>199</v>
       </c>
       <c r="D116" t="n">
-        <v>0.873015873015873</v>
+        <v>0.80241935483871</v>
       </c>
       <c r="E116" t="s">
         <v>16</v>
@@ -8203,16 +8123,16 @@
     </row>
     <row r="117">
       <c r="A117" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="B117" t="s">
         <v>15</v>
       </c>
       <c r="C117" t="n">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D117" t="n">
-        <v>0.805555555555556</v>
+        <v>0.870967741935484</v>
       </c>
       <c r="E117" t="s">
         <v>16</v>
@@ -8220,16 +8140,16 @@
     </row>
     <row r="118">
       <c r="A118" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="B118" t="s">
         <v>15</v>
       </c>
       <c r="C118" t="n">
-        <v>199</v>
+        <v>195</v>
       </c>
       <c r="D118" t="n">
-        <v>0.78968253968254</v>
+        <v>0.786290322580645</v>
       </c>
       <c r="E118" t="s">
         <v>16</v>
@@ -8237,16 +8157,16 @@
     </row>
     <row r="119">
       <c r="A119" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="B119" t="s">
         <v>15</v>
       </c>
       <c r="C119" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D119" t="n">
-        <v>0.76984126984127</v>
+        <v>0.766129032258065</v>
       </c>
       <c r="E119" t="s">
         <v>16</v>
@@ -8254,16 +8174,16 @@
     </row>
     <row r="120">
       <c r="A120" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="B120" t="s">
         <v>15</v>
       </c>
       <c r="C120" t="n">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="D120" t="n">
-        <v>0.876984126984127</v>
+        <v>0.875</v>
       </c>
       <c r="E120" t="s">
         <v>16</v>
@@ -8271,16 +8191,16 @@
     </row>
     <row r="121">
       <c r="A121" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="B121" t="s">
         <v>15</v>
       </c>
       <c r="C121" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D121" t="n">
-        <v>0.849206349206349</v>
+        <v>0.846774193548387</v>
       </c>
       <c r="E121" t="s">
         <v>16</v>
@@ -8288,16 +8208,16 @@
     </row>
     <row r="122">
       <c r="A122" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="B122" t="s">
         <v>15</v>
       </c>
       <c r="C122" t="n">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="D122" t="n">
-        <v>0.873015873015873</v>
+        <v>0.870967741935484</v>
       </c>
       <c r="E122" t="s">
         <v>16</v>
@@ -8305,16 +8225,16 @@
     </row>
     <row r="123">
       <c r="A123" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="B123" t="s">
         <v>15</v>
       </c>
       <c r="C123" t="n">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D123" t="n">
-        <v>0.801587301587302</v>
+        <v>0.806451612903226</v>
       </c>
       <c r="E123" t="s">
         <v>16</v>
@@ -8322,16 +8242,16 @@
     </row>
     <row r="124">
       <c r="A124" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="B124" t="s">
         <v>15</v>
       </c>
       <c r="C124" t="n">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D124" t="n">
-        <v>0.869047619047619</v>
+        <v>0.866935483870968</v>
       </c>
       <c r="E124" t="s">
         <v>16</v>
@@ -8339,16 +8259,16 @@
     </row>
     <row r="125">
       <c r="A125" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="B125" t="s">
         <v>15</v>
       </c>
       <c r="C125" t="n">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D125" t="n">
-        <v>0.718253968253968</v>
+        <v>0.721774193548387</v>
       </c>
       <c r="E125" t="s">
         <v>16</v>
@@ -8356,16 +8276,16 @@
     </row>
     <row r="126">
       <c r="A126" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="B126" t="s">
         <v>15</v>
       </c>
       <c r="C126" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="D126" t="n">
-        <v>0.849206349206349</v>
+        <v>0.846774193548387</v>
       </c>
       <c r="E126" t="s">
         <v>16</v>
@@ -8373,16 +8293,16 @@
     </row>
     <row r="127">
       <c r="A127" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="B127" t="s">
         <v>15</v>
       </c>
       <c r="C127" t="n">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="D127" t="n">
-        <v>0.726190476190476</v>
+        <v>0.725806451612903</v>
       </c>
       <c r="E127" t="s">
         <v>16</v>
@@ -8390,16 +8310,16 @@
     </row>
     <row r="128">
       <c r="A128" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="B128" t="s">
         <v>15</v>
       </c>
       <c r="C128" t="n">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D128" t="n">
-        <v>0.76984126984127</v>
+        <v>0.766129032258065</v>
       </c>
       <c r="E128" t="s">
         <v>16</v>
@@ -8407,16 +8327,16 @@
     </row>
     <row r="129">
       <c r="A129" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="B129" t="s">
         <v>15</v>
       </c>
       <c r="C129" t="n">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="D129" t="n">
-        <v>0.753968253968254</v>
+        <v>0.754032258064516</v>
       </c>
       <c r="E129" t="s">
         <v>16</v>
@@ -8424,16 +8344,16 @@
     </row>
     <row r="130">
       <c r="A130" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="B130" t="s">
         <v>15</v>
       </c>
       <c r="C130" t="n">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="D130" t="n">
-        <v>0.821428571428571</v>
+        <v>0.82258064516129</v>
       </c>
       <c r="E130" t="s">
         <v>16</v>
@@ -8441,16 +8361,16 @@
     </row>
     <row r="131">
       <c r="A131" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="B131" t="s">
         <v>15</v>
       </c>
       <c r="C131" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D131" t="n">
-        <v>0.825396825396825</v>
+        <v>0.82258064516129</v>
       </c>
       <c r="E131" t="s">
         <v>16</v>
@@ -8458,16 +8378,16 @@
     </row>
     <row r="132">
       <c r="A132" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="B132" t="s">
         <v>15</v>
       </c>
       <c r="C132" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="D132" t="n">
-        <v>0.817460317460317</v>
+        <v>0.814516129032258</v>
       </c>
       <c r="E132" t="s">
         <v>16</v>
@@ -8475,16 +8395,16 @@
     </row>
     <row r="133">
       <c r="A133" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="B133" t="s">
         <v>15</v>
       </c>
       <c r="C133" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D133" t="n">
-        <v>0.51984126984127</v>
+        <v>0.520161290322581</v>
       </c>
       <c r="E133" t="s">
         <v>16</v>
@@ -8492,16 +8412,16 @@
     </row>
     <row r="134">
       <c r="A134" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="B134" t="s">
         <v>15</v>
       </c>
       <c r="C134" t="n">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="D134" t="n">
-        <v>0.793650793650794</v>
+        <v>0.790322580645161</v>
       </c>
       <c r="E134" t="s">
         <v>16</v>
@@ -8509,16 +8429,16 @@
     </row>
     <row r="135">
       <c r="A135" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="B135" t="s">
         <v>15</v>
       </c>
       <c r="C135" t="n">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="D135" t="n">
-        <v>0.825396825396825</v>
+        <v>0.82258064516129</v>
       </c>
       <c r="E135" t="s">
         <v>16</v>
@@ -8526,16 +8446,16 @@
     </row>
     <row r="136">
       <c r="A136" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="B136" t="s">
         <v>15</v>
       </c>
       <c r="C136" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D136" t="n">
-        <v>0.761904761904762</v>
+        <v>0.758064516129032</v>
       </c>
       <c r="E136" t="s">
         <v>16</v>
@@ -8543,16 +8463,16 @@
     </row>
     <row r="137">
       <c r="A137" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="B137" t="s">
         <v>15</v>
       </c>
       <c r="C137" t="n">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="D137" t="n">
-        <v>0.71031746031746</v>
+        <v>0.709677419354839</v>
       </c>
       <c r="E137" t="s">
         <v>16</v>
@@ -8560,16 +8480,16 @@
     </row>
     <row r="138">
       <c r="A138" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="B138" t="s">
         <v>15</v>
       </c>
       <c r="C138" t="n">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D138" t="n">
-        <v>0.670634920634921</v>
+        <v>0.673387096774194</v>
       </c>
       <c r="E138" t="s">
         <v>16</v>
@@ -8577,16 +8497,16 @@
     </row>
     <row r="139">
       <c r="A139" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="B139" t="s">
         <v>15</v>
       </c>
       <c r="C139" t="n">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="D139" t="n">
-        <v>0.722222222222222</v>
+        <v>0.721774193548387</v>
       </c>
       <c r="E139" t="s">
         <v>16</v>
@@ -8594,16 +8514,16 @@
     </row>
     <row r="140">
       <c r="A140" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="B140" t="s">
         <v>15</v>
       </c>
       <c r="C140" t="n">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D140" t="n">
-        <v>0.634920634920635</v>
+        <v>0.633064516129032</v>
       </c>
       <c r="E140" t="s">
         <v>16</v>
@@ -8611,16 +8531,16 @@
     </row>
     <row r="141">
       <c r="A141" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="B141" t="s">
         <v>15</v>
       </c>
       <c r="C141" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="D141" t="n">
-        <v>0.71031746031746</v>
+        <v>0.705645161290323</v>
       </c>
       <c r="E141" t="s">
         <v>16</v>
@@ -8628,16 +8548,16 @@
     </row>
     <row r="142">
       <c r="A142" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="B142" t="s">
         <v>15</v>
       </c>
       <c r="C142" t="n">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="D142" t="n">
-        <v>0.825396825396825</v>
+        <v>0.826612903225806</v>
       </c>
       <c r="E142" t="s">
         <v>16</v>
@@ -8645,16 +8565,16 @@
     </row>
     <row r="143">
       <c r="A143" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="B143" t="s">
         <v>15</v>
       </c>
       <c r="C143" t="n">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="D143" t="n">
-        <v>0.603174603174603</v>
+        <v>0.604838709677419</v>
       </c>
       <c r="E143" t="s">
         <v>16</v>
@@ -8662,16 +8582,16 @@
     </row>
     <row r="144">
       <c r="A144" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="B144" t="s">
         <v>15</v>
       </c>
       <c r="C144" t="n">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="D144" t="n">
-        <v>0.702380952380952</v>
+        <v>0.745967741935484</v>
       </c>
       <c r="E144" t="s">
         <v>16</v>
@@ -8679,16 +8599,16 @@
     </row>
     <row r="145">
       <c r="A145" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="B145" t="s">
         <v>15</v>
       </c>
       <c r="C145" t="n">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="D145" t="n">
-        <v>0.781746031746032</v>
+        <v>0.782258064516129</v>
       </c>
       <c r="E145" t="s">
         <v>16</v>
@@ -8696,16 +8616,16 @@
     </row>
     <row r="146">
       <c r="A146" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="B146" t="s">
         <v>15</v>
       </c>
       <c r="C146" t="n">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="D146" t="n">
-        <v>0.75</v>
+        <v>0.701612903225806</v>
       </c>
       <c r="E146" t="s">
         <v>16</v>
@@ -8713,16 +8633,16 @@
     </row>
     <row r="147">
       <c r="A147" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="B147" t="s">
         <v>15</v>
       </c>
       <c r="C147" t="n">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="D147" t="n">
-        <v>0.761904761904762</v>
+        <v>0.758064516129032</v>
       </c>
       <c r="E147" t="s">
         <v>16</v>
@@ -8730,16 +8650,16 @@
     </row>
     <row r="148">
       <c r="A148" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="B148" t="s">
         <v>15</v>
       </c>
       <c r="C148" t="n">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="D148" t="n">
-        <v>0.634920634920635</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="E148" t="s">
         <v>16</v>
@@ -8747,16 +8667,16 @@
     </row>
     <row r="149">
       <c r="A149" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="B149" t="s">
         <v>15</v>
       </c>
       <c r="C149" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="D149" t="n">
-        <v>0.535714285714286</v>
+        <v>0.536290322580645</v>
       </c>
       <c r="E149" t="s">
         <v>16</v>
@@ -8764,16 +8684,16 @@
     </row>
     <row r="150">
       <c r="A150" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="B150" t="s">
         <v>15</v>
       </c>
       <c r="C150" t="n">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D150" t="n">
-        <v>0.630952380952381</v>
+        <v>0.629032258064516</v>
       </c>
       <c r="E150" t="s">
         <v>16</v>
@@ -8781,16 +8701,16 @@
     </row>
     <row r="151">
       <c r="A151" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="B151" t="s">
         <v>15</v>
       </c>
       <c r="C151" t="n">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D151" t="n">
-        <v>0.738095238095238</v>
+        <v>0.733870967741935</v>
       </c>
       <c r="E151" t="s">
         <v>16</v>
@@ -8798,16 +8718,16 @@
     </row>
     <row r="152">
       <c r="A152" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="B152" t="s">
         <v>15</v>
       </c>
       <c r="C152" t="n">
-        <v>110</v>
+        <v>98</v>
       </c>
       <c r="D152" t="n">
-        <v>0.436507936507937</v>
+        <v>0.395161290322581</v>
       </c>
       <c r="E152" t="s">
         <v>16</v>
@@ -8815,16 +8735,16 @@
     </row>
     <row r="153">
       <c r="A153" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="B153" t="s">
         <v>15</v>
       </c>
       <c r="C153" t="n">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="D153" t="n">
-        <v>0.396825396825397</v>
+        <v>0.435483870967742</v>
       </c>
       <c r="E153" t="s">
         <v>16</v>
@@ -8832,16 +8752,16 @@
     </row>
     <row r="154">
       <c r="A154" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="B154" t="s">
         <v>15</v>
       </c>
       <c r="C154" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D154" t="n">
-        <v>0.380952380952381</v>
+        <v>0.379032258064516</v>
       </c>
       <c r="E154" t="s">
         <v>16</v>
@@ -8849,16 +8769,16 @@
     </row>
     <row r="155">
       <c r="A155" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="B155" t="s">
         <v>15</v>
       </c>
       <c r="C155" t="n">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D155" t="n">
-        <v>0.472222222222222</v>
+        <v>0.471774193548387</v>
       </c>
       <c r="E155" t="s">
         <v>16</v>
@@ -8866,16 +8786,16 @@
     </row>
     <row r="156">
       <c r="A156" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="B156" t="s">
         <v>15</v>
       </c>
       <c r="C156" t="n">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="D156" t="n">
-        <v>0.507936507936508</v>
+        <v>0.508064516129032</v>
       </c>
       <c r="E156" t="s">
         <v>16</v>
@@ -8883,16 +8803,16 @@
     </row>
     <row r="157">
       <c r="A157" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="B157" t="s">
         <v>15</v>
       </c>
       <c r="C157" t="n">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="D157" t="n">
-        <v>0.408730158730159</v>
+        <v>0.435483870967742</v>
       </c>
       <c r="E157" t="s">
         <v>16</v>
@@ -8900,16 +8820,16 @@
     </row>
     <row r="158">
       <c r="A158" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="B158" t="s">
         <v>15</v>
       </c>
       <c r="C158" t="n">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="D158" t="n">
-        <v>0.44047619047619</v>
+        <v>0.407258064516129</v>
       </c>
       <c r="E158" t="s">
         <v>16</v>
@@ -8917,16 +8837,16 @@
     </row>
     <row r="159">
       <c r="A159" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="B159" t="s">
         <v>15</v>
       </c>
       <c r="C159" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D159" t="n">
-        <v>0.325396825396825</v>
+        <v>0.32258064516129</v>
       </c>
       <c r="E159" t="s">
         <v>16</v>
@@ -8934,16 +8854,16 @@
     </row>
     <row r="160">
       <c r="A160" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="B160" t="s">
         <v>15</v>
       </c>
       <c r="C160" t="n">
-        <v>144</v>
+        <v>141</v>
       </c>
       <c r="D160" t="n">
-        <v>0.571428571428571</v>
+        <v>0.568548387096774</v>
       </c>
       <c r="E160" t="s">
         <v>16</v>
@@ -8951,16 +8871,16 @@
     </row>
     <row r="161">
       <c r="A161" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="B161" t="s">
         <v>15</v>
       </c>
       <c r="C161" t="n">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D161" t="n">
-        <v>0.555555555555556</v>
+        <v>0.560483870967742</v>
       </c>
       <c r="E161" t="s">
         <v>16</v>
@@ -8968,16 +8888,16 @@
     </row>
     <row r="162">
       <c r="A162" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="B162" t="s">
         <v>15</v>
       </c>
       <c r="C162" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="D162" t="n">
-        <v>0.388888888888889</v>
+        <v>0.391129032258065</v>
       </c>
       <c r="E162" t="s">
         <v>16</v>
@@ -8985,13 +8905,13 @@
     </row>
     <row r="163">
       <c r="A163" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="B163" t="s">
         <v>15</v>
       </c>
       <c r="C163" t="n">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="D163" t="n">
         <v>0.5</v>
@@ -9002,16 +8922,16 @@
     </row>
     <row r="164">
       <c r="A164" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="B164" t="s">
         <v>15</v>
       </c>
       <c r="C164" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D164" t="n">
-        <v>0.301587301587302</v>
+        <v>0.30241935483871</v>
       </c>
       <c r="E164" t="s">
         <v>16</v>
@@ -9019,16 +8939,16 @@
     </row>
     <row r="165">
       <c r="A165" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="B165" t="s">
         <v>15</v>
       </c>
       <c r="C165" t="n">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D165" t="n">
-        <v>0.28968253968254</v>
+        <v>0.286290322580645</v>
       </c>
       <c r="E165" t="s">
         <v>16</v>
@@ -9036,16 +8956,16 @@
     </row>
     <row r="166">
       <c r="A166" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="B166" t="s">
         <v>15</v>
       </c>
       <c r="C166" t="n">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D166" t="n">
-        <v>0.464285714285714</v>
+        <v>0.467741935483871</v>
       </c>
       <c r="E166" t="s">
         <v>16</v>
@@ -9053,16 +8973,16 @@
     </row>
     <row r="167">
       <c r="A167" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="B167" t="s">
         <v>15</v>
       </c>
       <c r="C167" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D167" t="n">
-        <v>0.25</v>
+        <v>0.245967741935484</v>
       </c>
       <c r="E167" t="s">
         <v>16</v>
@@ -9070,16 +8990,16 @@
     </row>
     <row r="168">
       <c r="A168" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="B168" t="s">
         <v>15</v>
       </c>
       <c r="C168" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D168" t="n">
-        <v>0.257936507936508</v>
+        <v>0.258064516129032</v>
       </c>
       <c r="E168" t="s">
         <v>16</v>
@@ -9087,16 +9007,16 @@
     </row>
     <row r="169">
       <c r="A169" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="B169" t="s">
         <v>15</v>
       </c>
       <c r="C169" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D169" t="n">
-        <v>0.170634920634921</v>
+        <v>0.169354838709677</v>
       </c>
       <c r="E169" t="s">
         <v>16</v>
@@ -9104,16 +9024,16 @@
     </row>
     <row r="170">
       <c r="A170" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="B170" t="s">
         <v>15</v>
       </c>
       <c r="C170" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D170" t="n">
-        <v>0.242063492063492</v>
+        <v>0.237903225806452</v>
       </c>
       <c r="E170" t="s">
         <v>16</v>
@@ -9121,16 +9041,16 @@
     </row>
     <row r="171">
       <c r="A171" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="B171" t="s">
         <v>15</v>
       </c>
       <c r="C171" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D171" t="n">
-        <v>0.436507936507937</v>
+        <v>0.439516129032258</v>
       </c>
       <c r="E171" t="s">
         <v>16</v>
@@ -9138,16 +9058,16 @@
     </row>
     <row r="172">
       <c r="A172" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="B172" t="s">
         <v>15</v>
       </c>
       <c r="C172" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D172" t="n">
-        <v>0.448412698412698</v>
+        <v>0.44758064516129</v>
       </c>
       <c r="E172" t="s">
         <v>16</v>
@@ -9155,7 +9075,7 @@
     </row>
     <row r="173">
       <c r="A173" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="B173" t="s">
         <v>15</v>
@@ -9164,7 +9084,7 @@
         <v>49</v>
       </c>
       <c r="D173" t="n">
-        <v>0.194444444444444</v>
+        <v>0.19758064516129</v>
       </c>
       <c r="E173" t="s">
         <v>16</v>
@@ -9172,7 +9092,7 @@
     </row>
     <row r="174">
       <c r="A174" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="B174" t="s">
         <v>15</v>
@@ -9181,7 +9101,7 @@
         <v>30</v>
       </c>
       <c r="D174" t="n">
-        <v>0.119047619047619</v>
+        <v>0.120967741935484</v>
       </c>
       <c r="E174" t="s">
         <v>16</v>
@@ -9189,16 +9109,16 @@
     </row>
     <row r="175">
       <c r="A175" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="B175" t="s">
         <v>15</v>
       </c>
       <c r="C175" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D175" t="n">
-        <v>0.214285714285714</v>
+        <v>0.209677419354839</v>
       </c>
       <c r="E175" t="s">
         <v>16</v>
@@ -9206,16 +9126,16 @@
     </row>
     <row r="176">
       <c r="A176" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="B176" t="s">
         <v>15</v>
       </c>
       <c r="C176" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D176" t="n">
-        <v>0.420634920634921</v>
+        <v>0.423387096774194</v>
       </c>
       <c r="E176" t="s">
         <v>16</v>
@@ -9223,16 +9143,16 @@
     </row>
     <row r="177">
       <c r="A177" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="B177" t="s">
         <v>15</v>
       </c>
       <c r="C177" t="n">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D177" t="n">
-        <v>0.281746031746032</v>
+        <v>0.290322580645161</v>
       </c>
       <c r="E177" t="s">
         <v>16</v>
@@ -9240,13 +9160,13 @@
     </row>
     <row r="178">
       <c r="A178" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="B178" t="s">
         <v>15</v>
       </c>
       <c r="C178" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D178" t="n">
         <v>0.25</v>
@@ -9257,16 +9177,16 @@
     </row>
     <row r="179">
       <c r="A179" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="B179" t="s">
         <v>15</v>
       </c>
       <c r="C179" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="D179" t="n">
-        <v>0.242063492063492</v>
+        <v>0.241935483870968</v>
       </c>
       <c r="E179" t="s">
         <v>16</v>
@@ -9274,7 +9194,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="B180" t="s">
         <v>15</v>
@@ -9283,7 +9203,7 @@
         <v>67</v>
       </c>
       <c r="D180" t="n">
-        <v>0.265873015873016</v>
+        <v>0.270161290322581</v>
       </c>
       <c r="E180" t="s">
         <v>16</v>
@@ -9291,7 +9211,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="B181" t="s">
         <v>15</v>
@@ -9300,7 +9220,7 @@
         <v>1</v>
       </c>
       <c r="D181" t="n">
-        <v>0.00396825396825397</v>
+        <v>0.00403225806451613</v>
       </c>
       <c r="E181" t="s">
         <v>16</v>
@@ -9308,16 +9228,16 @@
     </row>
     <row r="182">
       <c r="A182" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="B182" t="s">
         <v>15</v>
       </c>
       <c r="C182" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D182" t="n">
-        <v>0.0634920634920635</v>
+        <v>0.0604838709677419</v>
       </c>
       <c r="E182" t="s">
         <v>16</v>
@@ -9325,7 +9245,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="B183" t="s">
         <v>15</v>
@@ -9334,7 +9254,7 @@
         <v>10</v>
       </c>
       <c r="D183" t="n">
-        <v>0.0396825396825397</v>
+        <v>0.0403225806451613</v>
       </c>
       <c r="E183" t="s">
         <v>16</v>
@@ -9342,7 +9262,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="B184" t="s">
         <v>15</v>
@@ -9351,7 +9271,7 @@
         <v>16</v>
       </c>
       <c r="D184" t="n">
-        <v>0.0634920634920635</v>
+        <v>0.0645161290322581</v>
       </c>
       <c r="E184" t="s">
         <v>16</v>
